--- a/workflow/automatic_pipeline_3_data_summary/equilibrium_global_history.xlsx
+++ b/workflow/automatic_pipeline_3_data_summary/equilibrium_global_history.xlsx
@@ -984,7 +984,7 @@
         <v>0.8463860263516095</v>
       </c>
       <c r="BE2" s="3" t="n">
-        <v>0.6022856187238481</v>
+        <v>0.6022666819111693</v>
       </c>
       <c r="BF2" s="3" t="n">
         <v>0.1087556818705518</v>
@@ -1123,7 +1123,7 @@
         <v>0.7437527167061088</v>
       </c>
       <c r="AM3" s="3" t="n">
-        <v>1.265456469567582</v>
+        <v>1.22634363353669</v>
       </c>
       <c r="AN3" s="3" t="n">
         <v>-0.3190220980110208</v>
@@ -1177,7 +1177,7 @@
         <v>0.8408077836841257</v>
       </c>
       <c r="BE3" s="3" t="n">
-        <v>0.7077142482728437</v>
+        <v>0.7531264477584095</v>
       </c>
       <c r="BF3" s="3" t="n">
         <v>0.1097322386091777</v>
@@ -1326,7 +1326,7 @@
         <v>0.06674344654944347</v>
       </c>
       <c r="AM4" s="3" t="n">
-        <v>1.743213703800086</v>
+        <v>2.059511750438172</v>
       </c>
       <c r="AN4" s="3" t="n">
         <v>-0.05385987822297611</v>
@@ -1380,7 +1380,7 @@
         <v>0.8416321999309841</v>
       </c>
       <c r="BE4" s="3" t="n">
-        <v>0.6540719916502918</v>
+        <v>1.214834837649617</v>
       </c>
       <c r="BF4" s="3" t="n">
         <v>0.0632478181358069</v>
@@ -1529,7 +1529,7 @@
         <v>0.7568764006991031</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>1.329999618377382</v>
+        <v>1.163066080991862</v>
       </c>
       <c r="AN5" s="3" t="n">
         <v>-0.2525434211869878</v>
@@ -1583,7 +1583,7 @@
         <v>0.8427852673308193</v>
       </c>
       <c r="BE5" s="3" t="n">
-        <v>0.5908918562593907</v>
+        <v>0.6243379823966652</v>
       </c>
       <c r="BF5" s="3" t="n">
         <v>0.1110586026786065</v>
@@ -1732,7 +1732,7 @@
         <v>0.3630158513450539</v>
       </c>
       <c r="AM6" s="3" t="n">
-        <v>1.585005225698805</v>
+        <v>1.557139008107417</v>
       </c>
       <c r="AN6" s="3" t="n">
         <v>-0.06104934248064853</v>
@@ -1786,7 +1786,7 @@
         <v>0.8516539792166804</v>
       </c>
       <c r="BE6" s="3" t="n">
-        <v>0.616870901458668</v>
+        <v>0.795161066498339</v>
       </c>
       <c r="BF6" s="3" t="n">
         <v>0.1036767047673784</v>
@@ -1935,7 +1935,7 @@
         <v>0.268456492216632</v>
       </c>
       <c r="AM7" s="3" t="n">
-        <v>1.60051848926256</v>
+        <v>1.620775518402028</v>
       </c>
       <c r="AN7" s="3" t="n">
         <v>-0.0732001209267833</v>
@@ -1989,7 +1989,7 @@
         <v>0.8517055641808893</v>
       </c>
       <c r="BE7" s="3" t="n">
-        <v>0.618007514483757</v>
+        <v>0.8571163342341395</v>
       </c>
       <c r="BF7" s="3" t="n">
         <v>0.09742483043839581</v>
@@ -2138,7 +2138,7 @@
         <v>0.1938231244752764</v>
       </c>
       <c r="AM8" s="3" t="n">
-        <v>1.628176858364199</v>
+        <v>1.722086091088337</v>
       </c>
       <c r="AN8" s="3" t="n">
         <v>-0.07540992698194338</v>
@@ -2192,7 +2192,7 @@
         <v>0.8558877084784577</v>
       </c>
       <c r="BE8" s="3" t="n">
-        <v>0.6332016021856077</v>
+        <v>0.9457026253972088</v>
       </c>
       <c r="BF8" s="3" t="n">
         <v>0.09283082302626007</v>
@@ -2341,7 +2341,7 @@
         <v>0.1373789902906288</v>
       </c>
       <c r="AM9" s="3" t="n">
-        <v>1.665836692164474</v>
+        <v>1.807308677457396</v>
       </c>
       <c r="AN9" s="3" t="n">
         <v>-0.06922120772820128</v>
@@ -2395,7 +2395,7 @@
         <v>0.8521028291922108</v>
       </c>
       <c r="BE9" s="3" t="n">
-        <v>0.6278265984928917</v>
+        <v>1.009000935239259</v>
       </c>
       <c r="BF9" s="3" t="n">
         <v>0.08342540491150344</v>
@@ -2544,7 +2544,7 @@
         <v>0.9467069561677012</v>
       </c>
       <c r="AM10" s="3" t="n">
-        <v>1.332731800040414</v>
+        <v>1.238795437114798</v>
       </c>
       <c r="AN10" s="3" t="n">
         <v>-0.2297431980182637</v>
@@ -2598,7 +2598,7 @@
         <v>0.8334696770684717</v>
       </c>
       <c r="BE10" s="3" t="n">
-        <v>0.6863625178947059</v>
+        <v>0.6873011361037223</v>
       </c>
       <c r="BF10" s="3" t="n">
         <v>0.1096079699132163</v>
@@ -2747,7 +2747,7 @@
         <v>0.7516663660336099</v>
       </c>
       <c r="AM11" s="3" t="n">
-        <v>1.35434926585588</v>
+        <v>1.298892478178744</v>
       </c>
       <c r="AN11" s="3" t="n">
         <v>-0.2260379529481055</v>
@@ -2801,7 +2801,7 @@
         <v>0.8427378572872861</v>
       </c>
       <c r="BE11" s="3" t="n">
-        <v>0.6855817218783</v>
+        <v>0.7347368217248562</v>
       </c>
       <c r="BF11" s="3" t="n">
         <v>0.1120243188104761</v>
@@ -2950,7 +2950,7 @@
         <v>0.6536011593840445</v>
       </c>
       <c r="AM12" s="3" t="n">
-        <v>1.346676403760503</v>
+        <v>1.351870905889701</v>
       </c>
       <c r="AN12" s="3" t="n">
         <v>-0.2451550881217489</v>
@@ -3004,7 +3004,7 @@
         <v>0.846929365258647</v>
       </c>
       <c r="BE12" s="3" t="n">
-        <v>0.7172894053083572</v>
+        <v>0.8011102480703246</v>
       </c>
       <c r="BF12" s="3" t="n">
         <v>0.1123553682777381</v>
@@ -3183,7 +3183,7 @@
         <v>0.8504167096985327</v>
       </c>
       <c r="BE13" s="3" t="n">
-        <v>0.7004797198918626</v>
+        <v>0.806541022707369</v>
       </c>
       <c r="BF13" s="3" t="n">
         <v>0.112422715965442</v>
@@ -3352,7 +3352,7 @@
         <v>0.8535358256226313</v>
       </c>
       <c r="BE14" s="3" t="n">
-        <v>0.7145149658569577</v>
+        <v>0.8400437946649152</v>
       </c>
       <c r="BF14" s="3" t="n">
         <v>0.1124068789950003</v>
@@ -3491,7 +3491,7 @@
         <v>0.3731517940985917</v>
       </c>
       <c r="AM15" s="3" t="n">
-        <v>1.590555551435921</v>
+        <v>1.787346287114419</v>
       </c>
       <c r="AN15" s="3" t="n">
         <v>-0.05174908653827781</v>
@@ -3545,7 +3545,7 @@
         <v>0.8587783788444828</v>
       </c>
       <c r="BE15" s="3" t="n">
-        <v>0.7901929630362626</v>
+        <v>1.017943054665598</v>
       </c>
       <c r="BF15" s="3" t="n">
         <v>0.1083318420866967</v>
@@ -3694,7 +3694,7 @@
         <v>0.1624730372396261</v>
       </c>
       <c r="AM16" s="3" t="n">
-        <v>1.643022606506657</v>
+        <v>2.010404657939371</v>
       </c>
       <c r="AN16" s="3" t="n">
         <v>-0.07632385927117513</v>
@@ -3748,7 +3748,7 @@
         <v>0.8613226320283545</v>
       </c>
       <c r="BE16" s="3" t="n">
-        <v>0.7864493617135631</v>
+        <v>1.22705528432163</v>
       </c>
       <c r="BF16" s="3" t="n">
         <v>0.09189192587996124</v>
@@ -3897,7 +3897,7 @@
         <v>0.09706830127528163</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>1.700344859748157</v>
+        <v>2.117054728760551</v>
       </c>
       <c r="AN17" s="3" t="n">
         <v>-0.06537973160659649</v>
@@ -3951,7 +3951,7 @@
         <v>0.8581275996389059</v>
       </c>
       <c r="BE17" s="3" t="n">
-        <v>0.7505485725060713</v>
+        <v>1.299572164689771</v>
       </c>
       <c r="BF17" s="3" t="n">
         <v>0.07941798976856182</v>
@@ -4100,7 +4100,7 @@
         <v>0.9057374934886866</v>
       </c>
       <c r="AM18" s="3" t="n">
-        <v>1.355653968288165</v>
+        <v>1.254018181214427</v>
       </c>
       <c r="AN18" s="3" t="n">
         <v>-0.20942704516845</v>
@@ -4154,7 +4154,7 @@
         <v>0.8373361514015085</v>
       </c>
       <c r="BE18" s="3" t="n">
-        <v>0.6717240173995362</v>
+        <v>0.6809047196545694</v>
       </c>
       <c r="BF18" s="3" t="n">
         <v>0.1114314748671482</v>
@@ -4303,7 +4303,7 @@
         <v>0.7950428438068712</v>
       </c>
       <c r="AM19" s="3" t="n">
-        <v>1.359361845067514</v>
+        <v>1.305709199454494</v>
       </c>
       <c r="AN19" s="3" t="n">
         <v>-0.2160624527834187</v>
@@ -4357,7 +4357,7 @@
         <v>0.8413702850293572</v>
       </c>
       <c r="BE19" s="3" t="n">
-        <v>0.6951257964659876</v>
+        <v>0.734059503312446</v>
       </c>
       <c r="BF19" s="3" t="n">
         <v>0.1122014042678274</v>
@@ -4506,7 +4506,7 @@
         <v>0.7027069407838469</v>
       </c>
       <c r="AM20" s="3" t="n">
-        <v>1.370705010305989</v>
+        <v>1.370977830646223</v>
       </c>
       <c r="AN20" s="3" t="n">
         <v>-0.2150247375947472</v>
@@ -4560,7 +4560,7 @@
         <v>0.8459309175000433</v>
       </c>
       <c r="BE20" s="3" t="n">
-        <v>0.7258662397591642</v>
+        <v>0.7931376942906017</v>
       </c>
       <c r="BF20" s="3" t="n">
         <v>0.1129687908441095</v>
@@ -4739,7 +4739,7 @@
         <v>0.8491229244933692</v>
       </c>
       <c r="BE21" s="3" t="n">
-        <v>0.748473073992111</v>
+        <v>0.8545824287204538</v>
       </c>
       <c r="BF21" s="3" t="n">
         <v>0.1120607166679667</v>
@@ -4908,7 +4908,7 @@
         <v>0.8534301741802274</v>
       </c>
       <c r="BE22" s="3" t="n">
-        <v>0.7651112042375063</v>
+        <v>0.907828501940031</v>
       </c>
       <c r="BF22" s="3" t="n">
         <v>0.1118290200899736</v>
@@ -5047,7 +5047,7 @@
         <v>0.3598998474384145</v>
       </c>
       <c r="AM23" s="3" t="n">
-        <v>1.586348235150164</v>
+        <v>1.863557773856168</v>
       </c>
       <c r="AN23" s="3" t="n">
         <v>-0.05917325465677181</v>
@@ -5101,7 +5101,7 @@
         <v>0.8599137740971201</v>
       </c>
       <c r="BE23" s="3" t="n">
-        <v>0.8513527983369801</v>
+        <v>1.099970283609472</v>
       </c>
       <c r="BF23" s="3" t="n">
         <v>0.1082930799895106</v>
@@ -5250,7 +5250,7 @@
         <v>0.1653938859009823</v>
       </c>
       <c r="AM24" s="3" t="n">
-        <v>1.641568777219378</v>
+        <v>2.129964715661604</v>
       </c>
       <c r="AN24" s="3" t="n">
         <v>-0.07615166867319534</v>
@@ -5304,7 +5304,7 @@
         <v>0.8603484699688329</v>
       </c>
       <c r="BE24" s="3" t="n">
-        <v>0.8700530148563181</v>
+        <v>1.347256161388512</v>
       </c>
       <c r="BF24" s="3" t="n">
         <v>0.09191491406745217</v>
@@ -5453,7 +5453,7 @@
         <v>0.1252206714213979</v>
       </c>
       <c r="AM25" s="3" t="n">
-        <v>1.672160665586526</v>
+        <v>2.219881528940474</v>
       </c>
       <c r="AN25" s="3" t="n">
         <v>-0.07098144303395026</v>
@@ -5507,7 +5507,7 @@
         <v>0.8600660369116586</v>
       </c>
       <c r="BE25" s="3" t="n">
-        <v>0.8637405196321047</v>
+        <v>1.419291917664186</v>
       </c>
       <c r="BF25" s="3" t="n">
         <v>0.08555050787566967</v>
@@ -5656,7 +5656,7 @@
         <v>0.8458484282007441</v>
       </c>
       <c r="AM26" s="3" t="n">
-        <v>1.356811842938669</v>
+        <v>1.276881425185829</v>
       </c>
       <c r="AN26" s="3" t="n">
         <v>-0.2136515969860151</v>
@@ -5710,7 +5710,7 @@
         <v>0.8393774884784508</v>
       </c>
       <c r="BE26" s="3" t="n">
-        <v>0.6809857712723588</v>
+        <v>0.7053013022095023</v>
       </c>
       <c r="BF26" s="3" t="n">
         <v>0.1118165048870953</v>
@@ -5859,7 +5859,7 @@
         <v>0.7544673296078761</v>
       </c>
       <c r="AM27" s="3" t="n">
-        <v>1.362452228532776</v>
+        <v>1.336647702291509</v>
       </c>
       <c r="AN27" s="3" t="n">
         <v>-0.2171618024903067</v>
@@ -5913,7 +5913,7 @@
         <v>0.843198639011329</v>
       </c>
       <c r="BE27" s="3" t="n">
-        <v>0.7135752207059408</v>
+        <v>0.7640024892702748</v>
       </c>
       <c r="BF27" s="3" t="n">
         <v>0.112447015462808</v>
@@ -6062,7 +6062,7 @@
         <v>0.6770810732545303</v>
       </c>
       <c r="AM28" s="3" t="n">
-        <v>1.3587832299602</v>
+        <v>1.394696811726337</v>
       </c>
       <c r="AN28" s="3" t="n">
         <v>-0.229942829975623</v>
@@ -6116,7 +6116,7 @@
         <v>0.8462878959149871</v>
       </c>
       <c r="BE28" s="3" t="n">
-        <v>0.7517663715153725</v>
+        <v>0.8302766117340488</v>
       </c>
       <c r="BF28" s="3" t="n">
         <v>0.1126698208471117</v>
@@ -6265,7 +6265,7 @@
         <v>0.6164955527328702</v>
       </c>
       <c r="AM29" s="3" t="n">
-        <v>1.373556564755642</v>
+        <v>1.453200472540879</v>
       </c>
       <c r="AN29" s="3" t="n">
         <v>-0.2234066503344223</v>
@@ -6319,7 +6319,7 @@
         <v>0.8501451399844151</v>
       </c>
       <c r="BE29" s="3" t="n">
-        <v>0.7743681273243319</v>
+        <v>0.8781255153302687</v>
       </c>
       <c r="BF29" s="3" t="n">
         <v>0.1130116429641538</v>
@@ -6468,7 +6468,7 @@
         <v>0.5703299205570619</v>
       </c>
       <c r="AM30" s="3" t="n">
-        <v>1.400919663567036</v>
+        <v>1.525011529817971</v>
       </c>
       <c r="AN30" s="3" t="n">
         <v>-0.2026916661800174</v>
@@ -6522,7 +6522,7 @@
         <v>0.8539536377426425</v>
       </c>
       <c r="BE30" s="3" t="n">
-        <v>0.8010109296247756</v>
+        <v>0.9258975311244616</v>
       </c>
       <c r="BF30" s="3" t="n">
         <v>0.1139078682094153</v>
@@ -6671,7 +6671,7 @@
         <v>0.3541865583153367</v>
       </c>
       <c r="AM31" s="3" t="n">
-        <v>1.585793441925793</v>
+        <v>1.956851164926873</v>
       </c>
       <c r="AN31" s="3" t="n">
         <v>-0.06141973962073222</v>
@@ -6725,7 +6725,7 @@
         <v>0.8634093921299003</v>
       </c>
       <c r="BE31" s="3" t="n">
-        <v>0.9210617933291301</v>
+        <v>1.194664313774342</v>
       </c>
       <c r="BF31" s="3" t="n">
         <v>0.1097103870276736</v>
@@ -6874,7 +6874,7 @@
         <v>0.06921416218874335</v>
       </c>
       <c r="AM32" s="3" t="n">
-        <v>1.740292291116157</v>
+        <v>2.327849274559127</v>
       </c>
       <c r="AN32" s="3" t="n">
         <v>-0.05399929748997145</v>
@@ -6928,7 +6928,7 @@
         <v>0.8391236136092077</v>
       </c>
       <c r="BE32" s="3" t="n">
-        <v>0.8049474429430081</v>
+        <v>1.484702777746034</v>
       </c>
       <c r="BF32" s="3" t="n">
         <v>0.06243198744394215</v>
@@ -7077,7 +7077,7 @@
         <v>0.9338843474452669</v>
       </c>
       <c r="AM33" s="3" t="n">
-        <v>1.36647102828889</v>
+        <v>1.147550278241877</v>
       </c>
       <c r="AN33" s="3" t="n">
         <v>-0.1993476435708434</v>
@@ -7131,7 +7131,7 @@
         <v>0.8396636997731931</v>
       </c>
       <c r="BE33" s="3" t="n">
-        <v>0.5707125787793014</v>
+        <v>0.5639885858828543</v>
       </c>
       <c r="BF33" s="3" t="n">
         <v>0.1114906883475456</v>
@@ -7280,7 +7280,7 @@
         <v>0.3884901388121397</v>
       </c>
       <c r="AM34" s="3" t="n">
-        <v>1.58541525368789</v>
+        <v>1.5185705625621</v>
       </c>
       <c r="AN34" s="3" t="n">
         <v>-0.05531544450251824</v>
@@ -7334,7 +7334,7 @@
         <v>0.8485649298189546</v>
       </c>
       <c r="BE34" s="3" t="n">
-        <v>0.5962630413209595</v>
+        <v>0.7535206579694144</v>
       </c>
       <c r="BF34" s="3" t="n">
         <v>0.1030968809348456</v>
@@ -7483,7 +7483,7 @@
         <v>0.07743927629715561</v>
       </c>
       <c r="AM35" s="3" t="n">
-        <v>1.728396107436289</v>
+        <v>1.826738692355688</v>
       </c>
       <c r="AN35" s="3" t="n">
         <v>-0.05650273166339614</v>
@@ -7537,7 +7537,7 @@
         <v>0.8413991028395634</v>
       </c>
       <c r="BE35" s="3" t="n">
-        <v>0.5482533914995924</v>
+        <v>0.9907920044692412</v>
       </c>
       <c r="BF35" s="3" t="n">
         <v>0.06610565322192076</v>
@@ -7686,7 +7686,7 @@
         <v>0.9832882688370144</v>
       </c>
       <c r="AM36" s="3" t="n">
-        <v>1.340155940653521</v>
+        <v>1.144589866719352</v>
       </c>
       <c r="AN36" s="3" t="n">
         <v>-0.2172471684875462</v>
@@ -7740,7 +7740,7 @@
         <v>0.8319464566981756</v>
       </c>
       <c r="BE36" s="3" t="n">
-        <v>0.5837229497612174</v>
+        <v>0.5831354806363649</v>
       </c>
       <c r="BF36" s="3" t="n">
         <v>0.1101136195580433</v>
@@ -7889,7 +7889,7 @@
         <v>0.6939043566312088</v>
       </c>
       <c r="AM37" s="3" t="n">
-        <v>1.375609076709747</v>
+        <v>1.270130063002279</v>
       </c>
       <c r="AN37" s="3" t="n">
         <v>-0.2103488415321397</v>
@@ -7943,7 +7943,7 @@
         <v>0.84601222626093</v>
       </c>
       <c r="BE37" s="3" t="n">
-        <v>0.6254934101167662</v>
+        <v>0.6874999454134755</v>
       </c>
       <c r="BF37" s="3" t="n">
         <v>0.113147327288761</v>
@@ -8092,7 +8092,7 @@
         <v>0.07669598391465163</v>
       </c>
       <c r="AM38" s="3" t="n">
-        <v>1.726946431181813</v>
+        <v>2.429443160077646</v>
       </c>
       <c r="AN38" s="3" t="n">
         <v>-0.05838016564217974</v>
@@ -8146,7 +8146,7 @@
         <v>0.8502948174467907</v>
       </c>
       <c r="BE38" s="3" t="n">
-        <v>0.880212600905265</v>
+        <v>1.595160027307829</v>
       </c>
       <c r="BF38" s="3" t="n">
         <v>0.07050608793405146</v>
@@ -8295,7 +8295,7 @@
         <v>0.1745909350731139</v>
       </c>
       <c r="AM39" s="3" t="n">
-        <v>1.604142924750602</v>
+        <v>1.670268351838397</v>
       </c>
       <c r="AN39" s="3" t="n">
         <v>-0.09046489375235589</v>
@@ -8349,7 +8349,7 @@
         <v>0.9155604340323352</v>
       </c>
       <c r="BE39" s="3" t="n">
-        <v>0.5950048553745931</v>
+        <v>0.913429336339274</v>
       </c>
       <c r="BF39" s="3" t="n">
         <v>0.1169181447264535</v>
@@ -8498,7 +8498,7 @@
         <v>0.04735544273803119</v>
       </c>
       <c r="AM40" s="3" t="n">
-        <v>1.77648278015253</v>
+        <v>1.919242553943117</v>
       </c>
       <c r="AN40" s="3" t="n">
         <v>-0.04792887749863173</v>
@@ -8552,7 +8552,7 @@
         <v>0.8429280556136945</v>
       </c>
       <c r="BE40" s="3" t="n">
-        <v>0.5317720085085196</v>
+        <v>1.054965602616168</v>
       </c>
       <c r="BF40" s="3" t="n">
         <v>0.05753777309851553</v>
@@ -8701,7 +8701,7 @@
         <v>0.1565012684223154</v>
       </c>
       <c r="AM41" s="3" t="n">
-        <v>1.649821193820209</v>
+        <v>1.858337149295857</v>
       </c>
       <c r="AN41" s="3" t="n">
         <v>-0.07278442118251116</v>
@@ -8755,7 +8755,7 @@
         <v>0.8555582448899111</v>
       </c>
       <c r="BE41" s="3" t="n">
-        <v>0.6821199203188479</v>
+        <v>1.069818762977009</v>
       </c>
       <c r="BF41" s="3" t="n">
         <v>0.08822142814286081</v>
@@ -8904,7 +8904,7 @@
         <v>0.03335198296894996</v>
       </c>
       <c r="AM42" s="3" t="n">
-        <v>1.80712646381841</v>
+        <v>2.547412150658409</v>
       </c>
       <c r="AN42" s="3" t="n">
         <v>-0.04198982422619568</v>
@@ -8958,7 +8958,7 @@
         <v>0.8412859614026846</v>
       </c>
       <c r="BE42" s="3" t="n">
-        <v>0.7844684038743704</v>
+        <v>1.664843830862302</v>
       </c>
       <c r="BF42" s="3" t="n">
         <v>0.05084807061395092</v>
@@ -9107,7 +9107,7 @@
         <v>0.04390270494943879</v>
       </c>
       <c r="AM43" s="3" t="n">
-        <v>1.782894046111641</v>
+        <v>2.079839919936731</v>
       </c>
       <c r="AN43" s="3" t="n">
         <v>-0.04701547286987784</v>
@@ -9161,7 +9161,7 @@
         <v>0.8448175174852121</v>
       </c>
       <c r="BE43" s="3" t="n">
-        <v>1.211573813877918</v>
+        <v>1.21190063331585</v>
       </c>
       <c r="BF43" s="3" t="n">
         <v>0.05760123131744739</v>
@@ -9310,7 +9310,7 @@
         <v>0.7019922948883381</v>
       </c>
       <c r="AM44" s="3" t="n">
-        <v>1.351327140312175</v>
+        <v>1.278870536504533</v>
       </c>
       <c r="AN44" s="3" t="n">
         <v>-0.2372300257777435</v>
@@ -9364,7 +9364,7 @@
         <v>0.845705541749697</v>
       </c>
       <c r="BE44" s="3" t="n">
-        <v>0.6662278540200883</v>
+        <v>0.7218219792373164</v>
       </c>
       <c r="BF44" s="3" t="n">
         <v>0.1118320079001721</v>
@@ -9513,7 +9513,7 @@
         <v>0.4080955163420294</v>
       </c>
       <c r="AM45" s="3" t="n">
-        <v>1.601477412384835</v>
+        <v>1.630029949298693</v>
       </c>
       <c r="AN45" s="3" t="n">
         <v>-0.03377679336823824</v>
@@ -9567,7 +9567,7 @@
         <v>0.8553722501905567</v>
       </c>
       <c r="BE45" s="3" t="n">
-        <v>0.6748240448281313</v>
+        <v>0.8461796397903952</v>
       </c>
       <c r="BF45" s="3" t="n">
         <v>0.1079134351354494</v>
@@ -9716,7 +9716,7 @@
         <v>0.1350345921795708</v>
       </c>
       <c r="AM46" s="3" t="n">
-        <v>1.66725495829333</v>
+        <v>1.911616877212901</v>
       </c>
       <c r="AN46" s="3" t="n">
         <v>-0.0692249404595221</v>
@@ -9770,7 +9770,7 @@
         <v>0.8529833145046327</v>
       </c>
       <c r="BE46" s="3" t="n">
-        <v>0.6852083493109028</v>
+        <v>1.112601868295997</v>
       </c>
       <c r="BF46" s="3" t="n">
         <v>0.08341841675562155</v>
@@ -9919,7 +9919,7 @@
         <v>0.3289125525758717</v>
       </c>
       <c r="AM47" s="3" t="n">
-        <v>1.586456106067676</v>
+        <v>1.792577396643016</v>
       </c>
       <c r="AN47" s="3" t="n">
         <v>-0.06952142065454359</v>
@@ -9973,7 +9973,7 @@
         <v>0.8579707258172359</v>
       </c>
       <c r="BE47" s="3" t="n">
-        <v>0.7857888880495292</v>
+        <v>1.03411005393645</v>
       </c>
       <c r="BF47" s="3" t="n">
         <v>0.1046797935997078</v>
@@ -10122,7 +10122,7 @@
         <v>0.1117531822239183</v>
       </c>
       <c r="AM48" s="3" t="n">
-        <v>1.686112362536151</v>
+        <v>1.988015284543084</v>
       </c>
       <c r="AN48" s="3" t="n">
         <v>-0.06793834886423589</v>
@@ -10176,7 +10176,7 @@
         <v>0.8583887306991147</v>
       </c>
       <c r="BE48" s="3" t="n">
-        <v>0.7036208175039284</v>
+        <v>1.178928277707126</v>
       </c>
       <c r="BF48" s="3" t="n">
         <v>0.08209774907964523</v>
@@ -10325,7 +10325,7 @@
         <v>0.9705177449893017</v>
       </c>
       <c r="AM49" s="3" t="n">
-        <v>1.262684477964677</v>
+        <v>0.9314374631164161</v>
       </c>
       <c r="AN49" s="3" t="n">
         <v>-0.2998637837903504</v>
@@ -10379,7 +10379,7 @@
         <v>0.8293407056577062</v>
       </c>
       <c r="BE49" s="3" t="n">
-        <v>0.4575306268348837</v>
+        <v>0.4500271160292528</v>
       </c>
       <c r="BF49" s="3" t="n">
         <v>0.1066643916445487</v>
@@ -10558,7 +10558,7 @@
         <v>0.8340546751939958</v>
       </c>
       <c r="BE50" s="3" t="n">
-        <v>0.4292550702366349</v>
+        <v>0.4568135744952252</v>
       </c>
       <c r="BF50" s="3" t="n">
         <v>0.1063936869167936</v>
@@ -10697,7 +10697,7 @@
         <v>0.4368378803309064</v>
       </c>
       <c r="AM51" s="3" t="n">
-        <v>1.580794098036871</v>
+        <v>1.26682421536639</v>
       </c>
       <c r="AN51" s="3" t="n">
         <v>-0.04907502982526935</v>
@@ -10751,7 +10751,7 @@
         <v>0.8386435366172701</v>
       </c>
       <c r="BE51" s="3" t="n">
-        <v>0.4053612612877519</v>
+        <v>0.5009646812605891</v>
       </c>
       <c r="BF51" s="3" t="n">
         <v>0.1001830118152053</v>
@@ -10900,7 +10900,7 @@
         <v>0.172836917210878</v>
       </c>
       <c r="AM52" s="3" t="n">
-        <v>1.649590868909265</v>
+        <v>1.438078795984647</v>
       </c>
       <c r="AN52" s="3" t="n">
         <v>-0.06447576148125211</v>
@@ -10954,7 +10954,7 @@
         <v>0.8228479826515039</v>
       </c>
       <c r="BE52" s="3" t="n">
-        <v>0.4204824509004872</v>
+        <v>0.64552124227064</v>
       </c>
       <c r="BF52" s="3" t="n">
         <v>0.07255267797015594</v>
@@ -11103,7 +11103,7 @@
         <v>0.8877373175398917</v>
       </c>
       <c r="AM53" s="3" t="n">
-        <v>1.911524845225152</v>
+        <v>1.51035735357643</v>
       </c>
       <c r="AN53" s="3" t="n">
         <v>0.3372483472903081</v>
@@ -11157,7 +11157,7 @@
         <v>0.8210074522317523</v>
       </c>
       <c r="BE53" s="3" t="n">
-        <v>0.380341269321624</v>
+        <v>0.3859707573186998</v>
       </c>
       <c r="BF53" s="3" t="n">
         <v>0.1001959061421283</v>
@@ -11306,7 +11306,7 @@
         <v>0.536318131333869</v>
       </c>
       <c r="AM54" s="3" t="n">
-        <v>1.594396225487577</v>
+        <v>1.108475602918967</v>
       </c>
       <c r="AN54" s="3" t="n">
         <v>-0.01795675849991873</v>
@@ -11360,7 +11360,7 @@
         <v>0.835397536990904</v>
       </c>
       <c r="BE54" s="3" t="n">
-        <v>0.272233815559368</v>
+        <v>0.3202558694251379</v>
       </c>
       <c r="BF54" s="3" t="n">
         <v>0.1019759085348175</v>
@@ -11509,7 +11509,7 @@
         <v>0.1626266685127017</v>
       </c>
       <c r="AM55" s="3" t="n">
-        <v>1.653857164533904</v>
+        <v>0.4987552308847617</v>
       </c>
       <c r="AN55" s="3" t="n">
         <v>-0.06581613298300293</v>
@@ -11563,7 +11563,7 @@
         <v>0.8332285359000553</v>
       </c>
       <c r="BE55" s="3" t="n">
-        <v>-0.2952717838303244</v>
+        <v>-0.2952652848906885</v>
       </c>
       <c r="BF55" s="3" t="n">
         <v>0.07681475675316049</v>
@@ -11712,7 +11712,7 @@
         <v>0.1648695624803929</v>
       </c>
       <c r="AM56" s="3" t="n">
-        <v>1.653244027306563</v>
+        <v>0.6141043462766099</v>
       </c>
       <c r="AN56" s="3" t="n">
         <v>-0.06535824523378198</v>
@@ -11766,7 +11766,7 @@
         <v>0.8304105345748232</v>
       </c>
       <c r="BE56" s="3" t="n">
-        <v>-0.1798327089736037</v>
+        <v>-0.1798385447597808</v>
       </c>
       <c r="BF56" s="3" t="n">
         <v>0.07557928277002468</v>
@@ -11915,7 +11915,7 @@
         <v>0.645288725865413</v>
       </c>
       <c r="AM57" s="3" t="n">
-        <v>1.591624642658061</v>
+        <v>0.9183644562370418</v>
       </c>
       <c r="AN57" s="3" t="n">
         <v>-0.01277118902283125</v>
@@ -11969,7 +11969,7 @@
         <v>0.8252302264172132</v>
       </c>
       <c r="BE57" s="3" t="n">
-        <v>0.1180788762535845</v>
+        <v>0.1289377294194268</v>
       </c>
       <c r="BF57" s="3" t="n">
         <v>0.09680546459550499</v>
@@ -12118,7 +12118,7 @@
         <v>0.1318264321505328</v>
       </c>
       <c r="AM58" s="3" t="n">
-        <v>1.678396559477229</v>
+        <v>-1.178123169939412</v>
       </c>
       <c r="AN58" s="3" t="n">
         <v>-0.06032234418529647</v>
@@ -12172,7 +12172,7 @@
         <v>0.8168566499659379</v>
       </c>
       <c r="BE58" s="3" t="n">
-        <v>-1.21494815932474</v>
+        <v>-1.987160277585378</v>
       </c>
       <c r="BF58" s="3" t="n">
         <v>0.06345258934021961</v>
@@ -12321,7 +12321,7 @@
         <v>0.8914736144681705</v>
       </c>
       <c r="AM59" s="3" t="n">
-        <v>1.228186158271152</v>
+        <v>0.4584154257335715</v>
       </c>
       <c r="AN59" s="3" t="n">
         <v>-0.3429866728643827</v>
@@ -12375,7 +12375,7 @@
         <v>0.8336999960171476</v>
       </c>
       <c r="BE59" s="3" t="n">
-        <v>0.01595481915103926</v>
+        <v>0.01581568303018708</v>
       </c>
       <c r="BF59" s="3" t="n">
         <v>0.1069947601352943</v>
@@ -12524,7 +12524,7 @@
         <v>0.2078780700689501</v>
       </c>
       <c r="AM60" s="3" t="n">
-        <v>1.631717727257402</v>
+        <v>-1.476316095370759</v>
       </c>
       <c r="AN60" s="3" t="n">
         <v>-0.06698157183503251</v>
@@ -12578,7 +12578,7 @@
         <v>0.8294126644697578</v>
       </c>
       <c r="BE60" s="3" t="n">
-        <v>-1.528196326068415</v>
+        <v>-2.258684173081943</v>
       </c>
       <c r="BF60" s="3" t="n">
         <v>0.07966776886227758</v>
@@ -12727,7 +12727,7 @@
         <v>0.9148659018945164</v>
       </c>
       <c r="AM61" s="3" t="n">
-        <v>1.339571335638102</v>
+        <v>1.362986451124968</v>
       </c>
       <c r="AN61" s="3" t="n">
         <v>-0.2229350162915342</v>
@@ -12781,7 +12781,7 @@
         <v>0.8338232690983831</v>
       </c>
       <c r="BE61" s="3" t="n">
-        <v>0.7848785538836085</v>
+        <v>0.8046682914516838</v>
       </c>
       <c r="BF61" s="3" t="n">
         <v>0.1106283544060651</v>
@@ -12960,7 +12960,7 @@
         <v>0.8440778807367381</v>
       </c>
       <c r="BE62" s="3" t="n">
-        <v>0.8525260473522395</v>
+        <v>0.9680639044858336</v>
       </c>
       <c r="BF62" s="3" t="n">
         <v>0.1112121619870425</v>
@@ -13129,7 +13129,7 @@
         <v>0.8520433819080093</v>
       </c>
       <c r="BE63" s="3" t="n">
-        <v>0.8637167338387464</v>
+        <v>1.058028958087469</v>
       </c>
       <c r="BF63" s="3" t="n">
         <v>0.1103027199041896</v>
@@ -13268,7 +13268,7 @@
         <v>0.2735313107259966</v>
       </c>
       <c r="AM64" s="3" t="n">
-        <v>1.586523320019479</v>
+        <v>2.01868213876959</v>
       </c>
       <c r="AN64" s="3" t="n">
         <v>-0.08199872482552273</v>
@@ -13322,7 +13322,7 @@
         <v>0.8620562870739505</v>
       </c>
       <c r="BE64" s="3" t="n">
-        <v>0.9048208684812986</v>
+        <v>1.266419841172611</v>
       </c>
       <c r="BF64" s="3" t="n">
         <v>0.1043886620708151</v>
@@ -13501,7 +13501,7 @@
         <v>0.8307040793589535</v>
       </c>
       <c r="BE65" s="3" t="n">
-        <v>0.7364337587976838</v>
+        <v>0.736433810926943</v>
       </c>
       <c r="BF65" s="3" t="n">
         <v>0.1069897665507757</v>
@@ -13636,7 +13636,7 @@
         <v>0.8401658900172074</v>
       </c>
       <c r="AM66" s="3" t="n">
-        <v>1.709243406834902</v>
+        <v>2.065554021559146</v>
       </c>
       <c r="AN66" s="3" t="n">
         <v>0.1415118517355112</v>
@@ -13689,7 +13689,9 @@
       <c r="BD66" s="3" t="n">
         <v>0.8164158170971976</v>
       </c>
-      <c r="BE66" s="3" t="inlineStr"/>
+      <c r="BE66" s="3" t="n">
+        <v>1.14017639227394</v>
+      </c>
       <c r="BF66" s="3" t="n">
         <v>0.1008189617767085</v>
       </c>
@@ -13837,7 +13839,7 @@
         <v>0.7695434991517747</v>
       </c>
       <c r="AM67" s="3" t="n">
-        <v>1.67191841039724</v>
+        <v>2.040359472373932</v>
       </c>
       <c r="AN67" s="3" t="n">
         <v>0.09615726612759135</v>
@@ -13890,7 +13892,9 @@
       <c r="BD67" s="3" t="n">
         <v>0.8204150510844913</v>
       </c>
-      <c r="BE67" s="3" t="inlineStr"/>
+      <c r="BE67" s="3" t="n">
+        <v>1.156321634111517</v>
+      </c>
       <c r="BF67" s="3" t="n">
         <v>0.1015655978738931</v>
       </c>
@@ -14034,7 +14038,7 @@
         <v>0.9232798494679691</v>
       </c>
       <c r="AM68" s="3" t="n">
-        <v>1.610448194443145</v>
+        <v>1.658390503227331</v>
       </c>
       <c r="AN68" s="3" t="n">
         <v>0.05208488391354593</v>
@@ -14087,7 +14091,9 @@
       <c r="BD68" s="3" t="n">
         <v>0.8036816860845635</v>
       </c>
-      <c r="BE68" s="3" t="inlineStr"/>
+      <c r="BE68" s="3" t="n">
+        <v>0.827123964048986</v>
+      </c>
       <c r="BF68" s="3" t="n">
         <v>0.09559830710801544</v>
       </c>
@@ -14235,7 +14241,7 @@
         <v>0.8795549401101983</v>
       </c>
       <c r="AM69" s="3" t="n">
-        <v>1.638853229570352</v>
+        <v>1.748387373117383</v>
       </c>
       <c r="AN69" s="3" t="n">
         <v>0.07605914529526492</v>
@@ -14288,7 +14294,9 @@
       <c r="BD69" s="3" t="n">
         <v>0.8095093058796975</v>
       </c>
-      <c r="BE69" s="3" t="inlineStr"/>
+      <c r="BE69" s="3" t="n">
+        <v>0.8909311856845743</v>
+      </c>
       <c r="BF69" s="3" t="n">
         <v>0.09809133785779771</v>
       </c>
@@ -14432,7 +14440,7 @@
         <v>0.9090099705632778</v>
       </c>
       <c r="AM70" s="3" t="n">
-        <v>1.166268741449237</v>
+        <v>1.216253308201519</v>
       </c>
       <c r="AN70" s="3" t="n">
         <v>-0.3961283388024762</v>
@@ -14485,7 +14493,9 @@
       <c r="BD70" s="3" t="n">
         <v>0.8266539086967297</v>
       </c>
-      <c r="BE70" s="3" t="inlineStr"/>
+      <c r="BE70" s="3" t="n">
+        <v>0.8311831068781386</v>
+      </c>
       <c r="BF70" s="3" t="n">
         <v>0.106996986291741</v>
       </c>
@@ -14633,7 +14643,7 @@
         <v>0.8174328259308909</v>
       </c>
       <c r="AM71" s="3" t="n">
-        <v>1.256135715412056</v>
+        <v>1.344083760339279</v>
       </c>
       <c r="AN71" s="3" t="n">
         <v>-0.3153444711598293</v>
@@ -14686,7 +14696,9 @@
       <c r="BD71" s="3" t="n">
         <v>0.8339152066974723</v>
       </c>
-      <c r="BE71" s="3" t="inlineStr"/>
+      <c r="BE71" s="3" t="n">
+        <v>0.8736881382131654</v>
+      </c>
       <c r="BF71" s="3" t="n">
         <v>0.1093248401837183</v>
       </c>
@@ -14830,7 +14842,7 @@
         <v>0.697199629947894</v>
       </c>
       <c r="AM72" s="3" t="n">
-        <v>1.341823863049592</v>
+        <v>1.437196944330471</v>
       </c>
       <c r="AN72" s="3" t="n">
         <v>-0.2428956182365418</v>
@@ -14883,7 +14895,9 @@
       <c r="BD72" s="3" t="n">
         <v>0.8435496328160476</v>
       </c>
-      <c r="BE72" s="3" t="inlineStr"/>
+      <c r="BE72" s="3" t="n">
+        <v>0.8877328219239463</v>
+      </c>
       <c r="BF72" s="3" t="n">
         <v>0.1121929078567035</v>
       </c>
@@ -15031,7 +15045,7 @@
         <v>0.5837835024589635</v>
       </c>
       <c r="AM73" s="3" t="n">
-        <v>1.441078783965566</v>
+        <v>1.620054334553559</v>
       </c>
       <c r="AN73" s="3" t="n">
         <v>-0.1607189708058636</v>
@@ -15084,7 +15098,9 @@
       <c r="BD73" s="3" t="n">
         <v>0.8564578527062826</v>
       </c>
-      <c r="BE73" s="3" t="inlineStr"/>
+      <c r="BE73" s="3" t="n">
+        <v>0.9798744279737078</v>
+      </c>
       <c r="BF73" s="3" t="n">
         <v>0.115576350526367</v>
       </c>
@@ -15232,7 +15248,7 @@
         <v>0.05791831654222163</v>
       </c>
       <c r="AM74" s="3" t="n">
-        <v>1.756022849530688</v>
+        <v>2.700374042613717</v>
       </c>
       <c r="AN74" s="3" t="n">
         <v>-0.0523714122836284</v>
@@ -15286,7 +15302,7 @@
         <v>0.8471194973035996</v>
       </c>
       <c r="BE74" s="3" t="n">
-        <v>1.848317791867874</v>
+        <v>1.848548323990187</v>
       </c>
       <c r="BF74" s="3" t="n">
         <v>0.06350090525064225</v>
@@ -15435,7 +15451,7 @@
         <v>0.912488208563628</v>
       </c>
       <c r="AM75" s="3" t="n">
-        <v>1.321253302566873</v>
+        <v>1.608184613859016</v>
       </c>
       <c r="AN75" s="3" t="n">
         <v>-0.2451634439484877</v>
@@ -15489,7 +15505,7 @@
         <v>0.8337914051836147</v>
       </c>
       <c r="BE75" s="3" t="n">
-        <v>1.058685098246056</v>
+        <v>1.070139684549823</v>
       </c>
       <c r="BF75" s="3" t="n">
         <v>0.1090998288272479</v>
@@ -15668,7 +15684,7 @@
         <v>0.8434008752576859</v>
       </c>
       <c r="BE76" s="3" t="n">
-        <v>1.056210981614079</v>
+        <v>1.168142364014053</v>
       </c>
       <c r="BF76" s="3" t="n">
         <v>0.1108155091358706</v>
@@ -15837,7 +15853,7 @@
         <v>0.8497802021929611</v>
       </c>
       <c r="BE77" s="3" t="n">
-        <v>1.049873566464207</v>
+        <v>1.243020602494914</v>
       </c>
       <c r="BF77" s="3" t="n">
         <v>0.110019831758887</v>
@@ -15976,7 +15992,7 @@
         <v>0.3404754010507481</v>
       </c>
       <c r="AM78" s="3" t="n">
-        <v>1.582854769688637</v>
+        <v>2.117686724893611</v>
       </c>
       <c r="AN78" s="3" t="n">
         <v>-0.06752175457717902</v>
@@ -16030,7 +16046,7 @@
         <v>0.8616348679422431</v>
       </c>
       <c r="BE78" s="3" t="n">
-        <v>1.031792033104042</v>
+        <v>1.360020217337882</v>
       </c>
       <c r="BF78" s="3" t="n">
         <v>0.1079734819508147</v>
@@ -16209,7 +16225,7 @@
         <v>0.8629013012126981</v>
       </c>
       <c r="BE79" s="3" t="n">
-        <v>0.7950452343026304</v>
+        <v>1.011637542223543</v>
       </c>
       <c r="BF79" s="3" t="n">
         <v>0.1118446493291273</v>
@@ -16348,7 +16364,7 @@
         <v>0.311135805947448</v>
       </c>
       <c r="AM80" s="3" t="n">
-        <v>1.578874866348607</v>
+        <v>1.91549118141305</v>
       </c>
       <c r="AN80" s="3" t="n">
         <v>-0.08043005245289292</v>
@@ -16402,7 +16418,7 @@
         <v>0.8650763367104052</v>
       </c>
       <c r="BE80" s="3" t="n">
-        <v>0.8678750385906094</v>
+        <v>1.166268774465193</v>
       </c>
       <c r="BF80" s="3" t="n">
         <v>0.1078565414104022</v>
@@ -16551,7 +16567,7 @@
         <v>0.1677976431240382</v>
       </c>
       <c r="AM81" s="3" t="n">
-        <v>1.63882426551041</v>
+        <v>2.227132411427862</v>
       </c>
       <c r="AN81" s="3" t="n">
         <v>-0.07773309159387165</v>
@@ -16605,7 +16621,7 @@
         <v>0.8625475430897389</v>
       </c>
       <c r="BE81" s="3" t="n">
-        <v>0.9347948612932061</v>
+        <v>1.446586824469593</v>
       </c>
       <c r="BF81" s="3" t="n">
         <v>0.09332124850974174</v>
@@ -16754,7 +16770,7 @@
         <v>0.09466437984736016</v>
       </c>
       <c r="AM82" s="3" t="n">
-        <v>1.702462041259956</v>
+        <v>2.246522412373833</v>
       </c>
       <c r="AN82" s="3" t="n">
         <v>-0.06539294175788757</v>
@@ -16808,7 +16824,7 @@
         <v>0.8596868886260742</v>
       </c>
       <c r="BE82" s="3" t="n">
-        <v>0.8175013230717143</v>
+        <v>1.427987862622798</v>
       </c>
       <c r="BF82" s="3" t="n">
         <v>0.07952690453738506</v>
@@ -16957,7 +16973,7 @@
         <v>0.02976397191465482</v>
       </c>
       <c r="AM83" s="3" t="n">
-        <v>1.818079183199042</v>
+        <v>2.909541654033071</v>
       </c>
       <c r="AN83" s="3" t="n">
         <v>-0.04002394929391151</v>
@@ -17011,7 +17027,7 @@
         <v>0.8441134104199874</v>
       </c>
       <c r="BE83" s="3" t="n">
-        <v>0.9355012244808236</v>
+        <v>2.020514037080505</v>
       </c>
       <c r="BF83" s="3" t="n">
         <v>0.05089220451393857</v>
@@ -17160,7 +17176,7 @@
         <v>0.686298885415995</v>
       </c>
       <c r="AM84" s="3" t="n">
-        <v>1.434548654450987</v>
+        <v>1.762043045762184</v>
       </c>
       <c r="AN84" s="3" t="n">
         <v>-0.1538749760567263</v>
@@ -17214,7 +17230,7 @@
         <v>0.8541548166954981</v>
       </c>
       <c r="BE84" s="3" t="n">
-        <v>1.022113475583908</v>
+        <v>1.121706206565054</v>
       </c>
       <c r="BF84" s="3" t="n">
         <v>0.1167137905283617</v>
@@ -17363,7 +17379,7 @@
         <v>0.5033161322601545</v>
       </c>
       <c r="AM85" s="3" t="n">
-        <v>1.453876038521935</v>
+        <v>1.876892277697606</v>
       </c>
       <c r="AN85" s="3" t="n">
         <v>-0.1611740423463168</v>
@@ -17417,7 +17433,7 @@
         <v>0.8605523054187414</v>
       </c>
       <c r="BE85" s="3" t="n">
-        <v>1.029829804287421</v>
+        <v>1.230541279609797</v>
       </c>
       <c r="BF85" s="3" t="n">
         <v>0.1150071137284382</v>
@@ -17566,7 +17582,7 @@
         <v>0.468625960076238</v>
       </c>
       <c r="AM86" s="3" t="n">
-        <v>1.492480564652671</v>
+        <v>1.712327878592207</v>
       </c>
       <c r="AN86" s="3" t="n">
         <v>-0.1274998284276794</v>
@@ -17620,7 +17636,7 @@
         <v>0.8653523448619834</v>
       </c>
       <c r="BE86" s="3" t="n">
-        <v>0.8435054635048826</v>
+        <v>1.029837510479711</v>
       </c>
       <c r="BF86" s="3" t="n">
         <v>0.1166521503947306</v>
@@ -17769,7 +17785,7 @@
         <v>0.283523302992521</v>
       </c>
       <c r="AM87" s="3" t="n">
-        <v>1.582663357842328</v>
+        <v>1.953326330431758</v>
       </c>
       <c r="AN87" s="3" t="n">
         <v>-0.08528258420479251</v>
@@ -17823,7 +17839,7 @@
         <v>0.8659855155276426</v>
       </c>
       <c r="BE87" s="3" t="n">
-        <v>0.8745345640697817</v>
+        <v>1.20463594361299</v>
       </c>
       <c r="BF87" s="3" t="n">
         <v>0.1063737316251808</v>
@@ -17972,7 +17988,7 @@
         <v>0.02325895373575377</v>
       </c>
       <c r="AM88" s="3" t="n">
-        <v>1.830411818860165</v>
+        <v>3.013254588950521</v>
       </c>
       <c r="AN88" s="3" t="n">
         <v>0.0009453725487855724</v>
@@ -18026,7 +18042,7 @@
         <v>0.1483555776361653</v>
       </c>
       <c r="BE88" s="3" t="n">
-        <v>0.9237013875109096</v>
+        <v>2.097575993246046</v>
       </c>
       <c r="BF88" s="3" t="n">
         <v>-0.374338907366925</v>
@@ -18175,7 +18191,7 @@
         <v>0.8587326075856829</v>
       </c>
       <c r="AM89" s="3" t="n">
-        <v>1.372710809221356</v>
+        <v>1.362631446714331</v>
       </c>
       <c r="AN89" s="3" t="n">
         <v>-0.1979013308583554</v>
@@ -18229,7 +18245,7 @@
         <v>0.8404263211467463</v>
       </c>
       <c r="BE89" s="3" t="n">
-        <v>0.7521976620024157</v>
+        <v>0.775226707532831</v>
       </c>
       <c r="BF89" s="3" t="n">
         <v>0.1120899085601474</v>
@@ -18378,7 +18394,7 @@
         <v>0.1086920102176522</v>
       </c>
       <c r="AM90" s="3" t="n">
-        <v>1.688821582290259</v>
+        <v>2.345225524560972</v>
       </c>
       <c r="AN90" s="3" t="n">
         <v>-0.06671009602310829</v>
@@ -18432,7 +18448,7 @@
         <v>0.8561083225495214</v>
       </c>
       <c r="BE90" s="3" t="n">
-        <v>0.8996592511699641</v>
+        <v>1.534169781427396</v>
       </c>
       <c r="BF90" s="3" t="n">
         <v>0.08058163029107665</v>
@@ -18581,7 +18597,7 @@
         <v>0.0251123934101774</v>
       </c>
       <c r="AM91" s="3" t="n">
-        <v>1.832244846187337</v>
+        <v>3.402513221633605</v>
       </c>
       <c r="AN91" s="3" t="n">
         <v>-0.03710942701854347</v>
@@ -18635,7 +18651,7 @@
         <v>0.8442767237759021</v>
       </c>
       <c r="BE91" s="3" t="n">
-        <v>1.12546712600917</v>
+        <v>2.504945512049209</v>
       </c>
       <c r="BF91" s="3" t="n">
         <v>0.0481103307635603</v>
@@ -18784,7 +18800,7 @@
         <v>0.6817473036511519</v>
       </c>
       <c r="AM92" s="3" t="n">
-        <v>1.434039421506356</v>
+        <v>1.727581975030042</v>
       </c>
       <c r="AN92" s="3" t="n">
         <v>-0.1550633923420691</v>
@@ -18838,7 +18854,7 @@
         <v>0.8541025107721927</v>
       </c>
       <c r="BE92" s="3" t="n">
-        <v>0.9900998233918532</v>
+        <v>1.088093960447899</v>
       </c>
       <c r="BF92" s="3" t="n">
         <v>0.1165342610059147</v>
@@ -18987,7 +19003,7 @@
         <v>0.4842869414808151</v>
       </c>
       <c r="AM93" s="3" t="n">
-        <v>1.474350967595082</v>
+        <v>1.707101787421285</v>
       </c>
       <c r="AN93" s="3" t="n">
         <v>-0.1438973131097111</v>
@@ -19041,7 +19057,7 @@
         <v>0.8630914782446567</v>
       </c>
       <c r="BE93" s="3" t="n">
-        <v>0.8614742144888431</v>
+        <v>1.0418749601786</v>
       </c>
       <c r="BF93" s="3" t="n">
         <v>0.1157217542878579</v>
@@ -19220,7 +19236,7 @@
         <v>0.8661389107655632</v>
       </c>
       <c r="BE94" s="3" t="n">
-        <v>0.7906864523968753</v>
+        <v>0.9918059412314321</v>
       </c>
       <c r="BF94" s="3" t="n">
         <v>0.1143061223625129</v>
@@ -19359,7 +19375,7 @@
         <v>0.02891407422167112</v>
       </c>
       <c r="AM95" s="3" t="n">
-        <v>1.820725850675261</v>
+        <v>2.968436515554973</v>
       </c>
       <c r="AN95" s="3" t="n">
         <v>-0.03917462074530365</v>
@@ -19413,7 +19429,7 @@
         <v>0.8416600190483278</v>
       </c>
       <c r="BE95" s="3" t="n">
-        <v>0.9535853469768615</v>
+        <v>2.077660900589995</v>
       </c>
       <c r="BF95" s="3" t="n">
         <v>0.04894663523114208</v>
@@ -19592,7 +19608,7 @@
         <v>0.8589068659369676</v>
       </c>
       <c r="BE96" s="3" t="n">
-        <v>0.7988755904830208</v>
+        <v>0.9618194095436227</v>
       </c>
       <c r="BF96" s="3" t="n">
         <v>0.1140089227714724</v>
@@ -19731,7 +19747,7 @@
         <v>0.2042565948087476</v>
       </c>
       <c r="AM97" s="3" t="n">
-        <v>1.619645393140355</v>
+        <v>1.848369434121363</v>
       </c>
       <c r="AN97" s="3" t="n">
         <v>-0.07852374762486147</v>
@@ -19785,7 +19801,7 @@
         <v>0.8598633421721518</v>
       </c>
       <c r="BE97" s="3" t="n">
-        <v>0.7256744394596732</v>
+        <v>1.077808611363616</v>
       </c>
       <c r="BF97" s="3" t="n">
         <v>0.09620672889168704</v>
@@ -19934,7 +19950,7 @@
         <v>0.06904776114010794</v>
       </c>
       <c r="AM98" s="3" t="n">
-        <v>1.73794941649973</v>
+        <v>2.23399780479077</v>
       </c>
       <c r="AN98" s="3" t="n">
         <v>-0.05610181764054667</v>
@@ -19988,7 +20004,7 @@
         <v>0.8487133622831671</v>
       </c>
       <c r="BE98" s="3" t="n">
-        <v>0.7485432923689039</v>
+        <v>1.393074005361179</v>
       </c>
       <c r="BF98" s="3" t="n">
         <v>0.06781591346364048</v>
@@ -20137,7 +20153,7 @@
         <v>0.6346393212000722</v>
       </c>
       <c r="AM99" s="3" t="n">
-        <v>1.415284694239352</v>
+        <v>1.786354415530531</v>
       </c>
       <c r="AN99" s="3" t="n">
         <v>-0.1805206049022143</v>
@@ -20191,7 +20207,7 @@
         <v>0.8526844872385014</v>
       </c>
       <c r="BE99" s="3" t="n">
-        <v>1.044537768406591</v>
+        <v>1.168972370861963</v>
       </c>
       <c r="BF99" s="3" t="n">
         <v>0.1144125056079347</v>
@@ -20370,7 +20386,7 @@
         <v>0.8656149402160024</v>
       </c>
       <c r="BE100" s="3" t="n">
-        <v>0.8746911770633581</v>
+        <v>1.139439273335568</v>
       </c>
       <c r="BF100" s="3" t="n">
         <v>0.1116490904517104</v>
@@ -20509,7 +20525,7 @@
         <v>0.2805913942231735</v>
       </c>
       <c r="AM101" s="3" t="n">
-        <v>1.585821297339964</v>
+        <v>1.97121608560193</v>
       </c>
       <c r="AN101" s="3" t="n">
         <v>-0.08311907011951591</v>
@@ -20563,7 +20579,7 @@
         <v>0.8645672628090942</v>
       </c>
       <c r="BE101" s="3" t="n">
-        <v>0.8830210705931325</v>
+        <v>1.219864971991706</v>
       </c>
       <c r="BF101" s="3" t="n">
         <v>0.1053920057094678</v>
@@ -20712,7 +20728,7 @@
         <v>0.1667119540065731</v>
       </c>
       <c r="AM102" s="3" t="n">
-        <v>1.640063860147658</v>
+        <v>2.125675656753823</v>
       </c>
       <c r="AN102" s="3" t="n">
         <v>-0.07715154467494056</v>
@@ -20766,7 +20782,7 @@
         <v>0.8620737978546615</v>
       </c>
       <c r="BE102" s="3" t="n">
-        <v>0.8650172725997392</v>
+        <v>1.344219499017464</v>
       </c>
       <c r="BF102" s="3" t="n">
         <v>0.09278466355551769</v>
@@ -20945,7 +20961,7 @@
         <v>0.8582414713404338</v>
       </c>
       <c r="BE103" s="3" t="n">
-        <v>1.010662009863731</v>
+        <v>1.222691411229868</v>
       </c>
       <c r="BF103" s="3" t="n">
         <v>0.1126051858356657</v>
@@ -21084,7 +21100,7 @@
         <v>0.2255684022923769</v>
       </c>
       <c r="AM104" s="3" t="n">
-        <v>1.606978764404459</v>
+        <v>2.004453876221227</v>
       </c>
       <c r="AN104" s="3" t="n">
         <v>-0.08231776948553482</v>
@@ -21138,7 +21154,7 @@
         <v>0.8636355937660228</v>
       </c>
       <c r="BE104" s="3" t="n">
-        <v>0.8568949284745756</v>
+        <v>1.242123378761764</v>
       </c>
       <c r="BF104" s="3" t="n">
         <v>0.1002025734089074</v>
@@ -21287,7 +21303,7 @@
         <v>0.02382970873858945</v>
       </c>
       <c r="AM105" s="3" t="n">
-        <v>1.814702588368348</v>
+        <v>2.632828354902832</v>
       </c>
       <c r="AN105" s="3" t="n">
         <v>0.003262137461623515</v>
@@ -21341,7 +21357,7 @@
         <v>0.1640176533143115</v>
       </c>
       <c r="BE105" s="3" t="n">
-        <v>0.7638462185978279</v>
+        <v>1.723845991987846</v>
       </c>
       <c r="BF105" s="3" t="n">
         <v>-0.3666918483615457</v>
@@ -21490,7 +21506,7 @@
         <v>0.3397805106861486</v>
       </c>
       <c r="AM106" s="3" t="n">
-        <v>1.583443795095433</v>
+        <v>1.920116275831037</v>
       </c>
       <c r="AN106" s="3" t="n">
         <v>-0.06805948069103362</v>
@@ -21544,7 +21560,7 @@
         <v>0.8617449285260794</v>
       </c>
       <c r="BE106" s="3" t="n">
-        <v>0.8855743793120704</v>
+        <v>1.162424118628837</v>
       </c>
       <c r="BF106" s="3" t="n">
         <v>0.1077099758012054</v>
@@ -21693,7 +21709,7 @@
         <v>0.08603053578597947</v>
       </c>
       <c r="AM107" s="3" t="n">
-        <v>1.712735026102504</v>
+        <v>2.106123784110714</v>
       </c>
       <c r="AN107" s="3" t="n">
         <v>-0.06329482947354537</v>
@@ -21747,7 +21763,7 @@
         <v>0.859013099466721</v>
       </c>
       <c r="BE107" s="3" t="n">
-        <v>0.7206359272539964</v>
+        <v>1.281403685796235</v>
       </c>
       <c r="BF107" s="3" t="n">
         <v>0.07743728986787002</v>
@@ -21896,7 +21912,7 @@
         <v>0.9883674262796724</v>
       </c>
       <c r="AM108" s="3" t="n">
-        <v>1.362481865495563</v>
+        <v>1.534806801980599</v>
       </c>
       <c r="AN108" s="3" t="n">
         <v>-0.1980224145539787</v>
@@ -21950,7 +21966,7 @@
         <v>0.8356114071846331</v>
       </c>
       <c r="BE108" s="3" t="n">
-        <v>0.9681238029884829</v>
+        <v>0.9525770765098071</v>
       </c>
       <c r="BF108" s="3" t="n">
         <v>0.1105393146336493</v>
@@ -22099,7 +22115,7 @@
         <v>0.4795372811264879</v>
       </c>
       <c r="AM109" s="3" t="n">
-        <v>1.464591682186101</v>
+        <v>1.661057064176267</v>
       </c>
       <c r="AN109" s="3" t="n">
         <v>-0.1531295170979499</v>
@@ -22153,7 +22169,7 @@
         <v>0.8615120550503594</v>
       </c>
       <c r="BE109" s="3" t="n">
-        <v>0.8245680788493093</v>
+        <v>1.005325981632191</v>
       </c>
       <c r="BF109" s="3" t="n">
         <v>0.1151926397114444</v>
@@ -22302,7 +22318,7 @@
         <v>0.07064974570974888</v>
       </c>
       <c r="AM110" s="3" t="n">
-        <v>1.735416003402555</v>
+        <v>2.253951129362219</v>
       </c>
       <c r="AN110" s="3" t="n">
         <v>-0.05704429380088627</v>
@@ -22356,7 +22372,7 @@
         <v>0.8506913279071815</v>
       </c>
       <c r="BE110" s="3" t="n">
-        <v>0.7623769097267875</v>
+        <v>1.414765274561385</v>
       </c>
       <c r="BF110" s="3" t="n">
         <v>0.06933273539118684</v>
@@ -22535,7 +22551,7 @@
         <v>0.8641794496141046</v>
       </c>
       <c r="BE111" s="3" t="n">
-        <v>0.790904949659924</v>
+        <v>0.9987028372553801</v>
       </c>
       <c r="BF111" s="3" t="n">
         <v>0.1128117584113673</v>
@@ -22674,7 +22690,7 @@
         <v>0.08904800067314231</v>
       </c>
       <c r="AM112" s="3" t="n">
-        <v>1.70945400869159</v>
+        <v>2.257027189772796</v>
       </c>
       <c r="AN112" s="3" t="n">
         <v>-0.06345083652725869</v>
@@ -22728,7 +22744,7 @@
         <v>0.8576631509647682</v>
       </c>
       <c r="BE112" s="3" t="n">
-        <v>0.8126517306255339</v>
+        <v>1.43402560369063</v>
       </c>
       <c r="BF112" s="3" t="n">
         <v>0.07728192566012865</v>
@@ -22877,7 +22893,7 @@
         <v>0.9850696261134255</v>
       </c>
       <c r="AM113" s="3" t="n">
-        <v>1.376567659970898</v>
+        <v>1.551417171013012</v>
       </c>
       <c r="AN113" s="3" t="n">
         <v>-0.1839073793068101</v>
@@ -22931,7 +22947,7 @@
         <v>0.8379397229774685</v>
       </c>
       <c r="BE113" s="3" t="n">
-        <v>0.9676101209631414</v>
+        <v>0.9550870306809678</v>
       </c>
       <c r="BF113" s="3" t="n">
         <v>0.1119036036310182</v>
@@ -23080,7 +23096,7 @@
         <v>0.627816827217609</v>
       </c>
       <c r="AM114" s="3" t="n">
-        <v>1.410120827390645</v>
+        <v>1.80769195512986</v>
       </c>
       <c r="AN114" s="3" t="n">
         <v>-0.1865966170514136</v>
@@ -23134,7 +23150,7 @@
         <v>0.852400051102396</v>
       </c>
       <c r="BE114" s="3" t="n">
-        <v>1.063452232714686</v>
+        <v>1.195929849960244</v>
       </c>
       <c r="BF114" s="3" t="n">
         <v>0.1141224081958986</v>
@@ -23283,7 +23299,7 @@
         <v>0.4757357585407223</v>
       </c>
       <c r="AM115" s="3" t="n">
-        <v>1.454320732932927</v>
+        <v>1.677780623688599</v>
       </c>
       <c r="AN115" s="3" t="n">
         <v>-0.1640856207662279</v>
@@ -23337,7 +23353,7 @@
         <v>0.8608406514306757</v>
       </c>
       <c r="BE115" s="3" t="n">
-        <v>0.8460504845250151</v>
+        <v>1.032663067605249</v>
       </c>
       <c r="BF115" s="3" t="n">
         <v>0.1147234983971765</v>
@@ -23486,7 +23502,7 @@
         <v>0.08065770643845688</v>
       </c>
       <c r="AM116" s="3" t="n">
-        <v>1.720681499078402</v>
+        <v>2.207989626036393</v>
       </c>
       <c r="AN116" s="3" t="n">
         <v>-0.06089118837391894</v>
@@ -23540,7 +23556,7 @@
         <v>0.8557728893084584</v>
       </c>
       <c r="BE116" s="3" t="n">
-        <v>0.7612657064898943</v>
+        <v>1.378094470684151</v>
       </c>
       <c r="BF116" s="3" t="n">
         <v>0.07440771350244506</v>
@@ -23689,7 +23705,7 @@
         <v>0.8577764487272368</v>
       </c>
       <c r="AM117" s="3" t="n">
-        <v>1.400409134890986</v>
+        <v>1.543046276920679</v>
       </c>
       <c r="AN117" s="3" t="n">
         <v>-0.1704124643962358</v>
@@ -23743,7 +23759,7 @@
         <v>0.845124367058999</v>
       </c>
       <c r="BE117" s="3" t="n">
-        <v>0.901589990660143</v>
+        <v>0.9280479416733046</v>
       </c>
       <c r="BF117" s="3" t="n">
         <v>0.1145346434865308</v>
@@ -23892,7 +23908,7 @@
         <v>0.5103809799323883</v>
       </c>
       <c r="AM118" s="3" t="n">
-        <v>1.440855191239243</v>
+        <v>1.634851031640344</v>
       </c>
       <c r="AN118" s="3" t="n">
         <v>-0.1725229118341279</v>
@@ -23946,7 +23962,7 @@
         <v>0.8590944959540252</v>
       </c>
       <c r="BE118" s="3" t="n">
-        <v>0.8383172609833832</v>
+        <v>1.000684891937786</v>
       </c>
       <c r="BF118" s="3" t="n">
         <v>0.1145796965076407</v>
@@ -24095,7 +24111,7 @@
         <v>0.6676790044163351</v>
       </c>
       <c r="AM119" s="3" t="n">
-        <v>1.412836563553614</v>
+        <v>1.222326667667011</v>
       </c>
       <c r="AN119" s="3" t="n">
         <v>-0.1778196068833328</v>
@@ -24149,7 +24165,7 @@
         <v>0.851049621732207</v>
       </c>
       <c r="BE119" s="3" t="n">
-        <v>0.5467184859237423</v>
+        <v>0.6048181893318704</v>
       </c>
       <c r="BF119" s="3" t="n">
         <v>0.1146994536140418</v>
@@ -24298,7 +24314,7 @@
         <v>0.3804123213697649</v>
       </c>
       <c r="AM120" s="3" t="n">
-        <v>1.600250369691025</v>
+        <v>1.376457480640334</v>
       </c>
       <c r="AN120" s="3" t="n">
         <v>-0.03971738708617634</v>
@@ -24352,7 +24368,7 @@
         <v>0.8601755110163011</v>
       </c>
       <c r="BE120" s="3" t="n">
-        <v>0.4638766028396659</v>
+        <v>0.5961909893379096</v>
       </c>
       <c r="BF120" s="3" t="n">
         <v>0.1095637128448923</v>
@@ -24501,7 +24517,7 @@
         <v>0.3448260949261771</v>
       </c>
       <c r="AM121" s="3" t="n">
-        <v>1.58172263613414</v>
+        <v>1.308352597369039</v>
       </c>
       <c r="AN121" s="3" t="n">
         <v>-0.06747112700829694</v>
@@ -24555,7 +24571,7 @@
         <v>0.8643956960185639</v>
       </c>
       <c r="BE121" s="3" t="n">
-        <v>0.4186784991756098</v>
+        <v>0.5512268428061173</v>
       </c>
       <c r="BF121" s="3" t="n">
         <v>0.1097902724889789</v>
@@ -24734,7 +24750,7 @@
         <v>0.8677298600997516</v>
       </c>
       <c r="BE122" s="3" t="n">
-        <v>0.3857917574918552</v>
+        <v>0.5026088703041349</v>
       </c>
       <c r="BF122" s="3" t="n">
         <v>0.1122762111803876</v>
@@ -24873,7 +24889,7 @@
         <v>0.1759514369968185</v>
       </c>
       <c r="AM123" s="3" t="n">
-        <v>1.633637740703439</v>
+        <v>1.258994781618305</v>
       </c>
       <c r="AN123" s="3" t="n">
         <v>-0.07863015067577461</v>
@@ -24927,7 +24943,7 @@
         <v>0.8627149143100772</v>
       </c>
       <c r="BE123" s="3" t="n">
-        <v>0.3131963523675883</v>
+        <v>0.4814909866044721</v>
       </c>
       <c r="BF123" s="3" t="n">
         <v>0.09444309454452531</v>
@@ -25076,7 +25092,7 @@
         <v>0.4909434815463712</v>
       </c>
       <c r="AM124" s="3" t="n">
-        <v>1.437083617169934</v>
+        <v>1.301485591558382</v>
       </c>
       <c r="AN124" s="3" t="n">
         <v>-0.1796403845418887</v>
@@ -25130,7 +25146,7 @@
         <v>0.8597519424046548</v>
       </c>
       <c r="BE124" s="3" t="n">
-        <v>0.5598564643045959</v>
+        <v>0.6727639752443596</v>
       </c>
       <c r="BF124" s="3" t="n">
         <v>0.1143625366497388</v>
@@ -25279,7 +25295,7 @@
         <v>0.5491255169545122</v>
       </c>
       <c r="AM125" s="3" t="n">
-        <v>1.4659957817369</v>
+        <v>1.270641312031407</v>
       </c>
       <c r="AN125" s="3" t="n">
         <v>-0.1402511198947262</v>
@@ -25333,7 +25349,7 @@
         <v>0.8610398513990792</v>
       </c>
       <c r="BE125" s="3" t="n">
-        <v>0.520183424798447</v>
+        <v>0.6077689811103202</v>
       </c>
       <c r="BF125" s="3" t="n">
         <v>0.1171362379578378</v>
@@ -25512,7 +25528,7 @@
         <v>0.8643551168404388</v>
       </c>
       <c r="BE126" s="3" t="n">
-        <v>0.5045760566878612</v>
+        <v>0.6506662509289495</v>
       </c>
       <c r="BF126" s="3" t="n">
         <v>0.1106143075253653</v>
@@ -25651,7 +25667,7 @@
         <v>0.161817759967084</v>
       </c>
       <c r="AM127" s="3" t="n">
-        <v>1.644233270708145</v>
+        <v>1.391052761163476</v>
       </c>
       <c r="AN127" s="3" t="n">
         <v>-0.07575050134939143</v>
@@ -25705,7 +25721,7 @@
         <v>0.8604158428101442</v>
       </c>
       <c r="BE127" s="3" t="n">
-        <v>0.3888744473152545</v>
+        <v>0.6068113764840997</v>
       </c>
       <c r="BF127" s="3" t="n">
         <v>0.09137765132653689</v>
@@ -25854,7 +25870,7 @@
         <v>0.6693079374024976</v>
       </c>
       <c r="AM128" s="3" t="n">
-        <v>1.403615399952299</v>
+        <v>1.225652799129679</v>
       </c>
       <c r="AN128" s="3" t="n">
         <v>-0.1867515498054919</v>
@@ -25908,7 +25924,7 @@
         <v>0.8498888292404562</v>
       </c>
       <c r="BE128" s="3" t="n">
-        <v>0.5580734317923213</v>
+        <v>0.6172208740562756</v>
       </c>
       <c r="BF128" s="3" t="n">
         <v>0.1141830944034427</v>
@@ -26057,7 +26073,7 @@
         <v>0.5550665569720313</v>
       </c>
       <c r="AM129" s="3" t="n">
-        <v>1.414386238478403</v>
+        <v>1.19886023554096</v>
       </c>
       <c r="AN129" s="3" t="n">
         <v>-0.1915786400851468</v>
@@ -26111,7 +26127,7 @@
         <v>0.8553400625510252</v>
       </c>
       <c r="BE129" s="3" t="n">
-        <v>0.5040532881519267</v>
+        <v>0.587456436344332</v>
       </c>
       <c r="BF129" s="3" t="n">
         <v>0.1141801092596043</v>
@@ -26260,7 +26276,7 @@
         <v>0.5522856923247678</v>
       </c>
       <c r="AM130" s="3" t="n">
-        <v>1.45483069944931</v>
+        <v>1.224658048597987</v>
       </c>
       <c r="AN130" s="3" t="n">
         <v>-0.1511953665460926</v>
@@ -26314,7 +26330,7 @@
         <v>0.8593511524154552</v>
       </c>
       <c r="BE130" s="3" t="n">
-        <v>0.4903865009236998</v>
+        <v>0.5728403821463782</v>
       </c>
       <c r="BF130" s="3" t="n">
         <v>0.1162730315065809</v>
@@ -26463,7 +26479,7 @@
         <v>0.306268090821593</v>
       </c>
       <c r="AM131" s="3" t="n">
-        <v>1.583815545066358</v>
+        <v>1.416308998561732</v>
       </c>
       <c r="AN131" s="3" t="n">
         <v>-0.07669777652226628</v>
@@ -26517,7 +26533,7 @@
         <v>0.8618329434638083</v>
       </c>
       <c r="BE131" s="3" t="n">
-        <v>0.4895601241861072</v>
+        <v>0.6627501142896863</v>
       </c>
       <c r="BF131" s="3" t="n">
         <v>0.1057851546445489</v>
@@ -26666,7 +26682,7 @@
         <v>0.1251858833664474</v>
       </c>
       <c r="AM132" s="3" t="n">
-        <v>1.673146530997239</v>
+        <v>1.319524669548384</v>
       </c>
       <c r="AN132" s="3" t="n">
         <v>-0.0699143839561277</v>
@@ -26720,7 +26736,7 @@
         <v>0.8574409365607784</v>
       </c>
       <c r="BE132" s="3" t="n">
-        <v>0.3129398927550215</v>
+        <v>0.5179085960278286</v>
       </c>
       <c r="BF132" s="3" t="n">
         <v>0.08436319341193678</v>
@@ -26869,7 +26885,7 @@
         <v>0.8119272124147393</v>
       </c>
       <c r="AM133" s="3" t="n">
-        <v>1.400292948061028</v>
+        <v>1.292088106350532</v>
       </c>
       <c r="AN133" s="3" t="n">
         <v>-0.174263080660893</v>
@@ -26923,7 +26939,7 @@
         <v>0.8457572343160752</v>
       </c>
       <c r="BE133" s="3" t="n">
-        <v>0.6481844007728448</v>
+        <v>0.6790731726504641</v>
       </c>
       <c r="BF133" s="3" t="n">
         <v>0.1145483352015499</v>
@@ -27072,7 +27088,7 @@
         <v>0.549090685912594</v>
       </c>
       <c r="AM134" s="3" t="n">
-        <v>1.460791012101174</v>
+        <v>1.305179948594989</v>
       </c>
       <c r="AN134" s="3" t="n">
         <v>-0.1446028402707257</v>
@@ -27126,7 +27142,7 @@
         <v>0.8596633802800355</v>
       </c>
       <c r="BE134" s="3" t="n">
-        <v>0.5502425074312672</v>
+        <v>0.6470858626797653</v>
       </c>
       <c r="BF134" s="3" t="n">
         <v>0.1167806876288604</v>
@@ -27275,7 +27291,7 @@
         <v>0.3601244698293492</v>
       </c>
       <c r="AM135" s="3" t="n">
-        <v>1.591122230120791</v>
+        <v>1.46355637741609</v>
       </c>
       <c r="AN135" s="3" t="n">
         <v>-0.0537982921528366</v>
@@ -27329,7 +27345,7 @@
         <v>0.8637646657712016</v>
       </c>
       <c r="BE135" s="3" t="n">
-        <v>0.5320402974348681</v>
+        <v>0.6948944084321126</v>
       </c>
       <c r="BF135" s="3" t="n">
         <v>0.1104368629816301</v>
@@ -27478,7 +27494,7 @@
         <v>0.1570401141857528</v>
       </c>
       <c r="AM136" s="3" t="n">
-        <v>1.64673391114372</v>
+        <v>1.420395527481948</v>
       </c>
       <c r="AN136" s="3" t="n">
         <v>-0.07518920715000166</v>
@@ -27532,7 +27548,7 @@
         <v>0.8598191759537356</v>
       </c>
       <c r="BE136" s="3" t="n">
-        <v>0.4006399853352302</v>
+        <v>0.6346231754850888</v>
       </c>
       <c r="BF136" s="3" t="n">
         <v>0.09067339212026794</v>
@@ -27681,7 +27697,7 @@
         <v>0.05785425407937542</v>
       </c>
       <c r="AM137" s="3" t="n">
-        <v>1.754616946610785</v>
+        <v>1.30343522377566</v>
       </c>
       <c r="AN137" s="3" t="n">
         <v>-0.05371043091180738</v>
@@ -27735,7 +27751,7 @@
         <v>0.8525604653023021</v>
       </c>
       <c r="BE137" s="3" t="n">
-        <v>0.2337973126530325</v>
+        <v>0.4529819659261715</v>
       </c>
       <c r="BF137" s="3" t="n">
         <v>0.06667161444226513</v>
@@ -27884,7 +27900,7 @@
         <v>0.3415160881859761</v>
       </c>
       <c r="AM138" s="3" t="n">
-        <v>1.58166792784837</v>
+        <v>1.398251003641728</v>
       </c>
       <c r="AN138" s="3" t="n">
         <v>-0.06827219981394517</v>
@@ -27938,7 +27954,7 @@
         <v>0.8631207447364532</v>
       </c>
       <c r="BE138" s="3" t="n">
-        <v>0.4879289053668609</v>
+        <v>0.6415531396245158</v>
       </c>
       <c r="BF138" s="3" t="n">
         <v>0.1089520512761791</v>
@@ -28087,7 +28103,7 @@
         <v>0.06579129714453444</v>
       </c>
       <c r="AM139" s="3" t="n">
-        <v>1.742901551566751</v>
+        <v>0.9982878880706139</v>
       </c>
       <c r="AN139" s="3" t="n">
         <v>-0.05535429379553425</v>
@@ -28141,7 +28157,7 @@
         <v>0.8492815344132826</v>
       </c>
       <c r="BE139" s="3" t="n">
-        <v>0.08237005054564474</v>
+        <v>0.1545142591850053</v>
       </c>
       <c r="BF139" s="3" t="n">
         <v>0.06718234656983613</v>
@@ -28290,7 +28306,7 @@
         <v>0.8233671370451104</v>
       </c>
       <c r="AM140" s="3" t="n">
-        <v>1.20702022022455</v>
+        <v>0.783996891464217</v>
       </c>
       <c r="AN140" s="3" t="n">
         <v>-0.3670433406673068</v>
@@ -28344,7 +28360,7 @@
         <v>0.8331988703483327</v>
       </c>
       <c r="BE140" s="3" t="n">
-        <v>0.3476311501887291</v>
+        <v>0.3640084516855954</v>
       </c>
       <c r="BF140" s="3" t="n">
         <v>0.1079046638018181</v>
@@ -28493,7 +28509,7 @@
         <v>0.6913559540192574</v>
       </c>
       <c r="AM141" s="3" t="n">
-        <v>1.291325132795566</v>
+        <v>0.8237864321020379</v>
       </c>
       <c r="AN141" s="3" t="n">
         <v>-0.2957559996962548</v>
@@ -28547,7 +28563,7 @@
         <v>0.8423178682545565</v>
       </c>
       <c r="BE141" s="3" t="n">
-        <v>0.2956204113195523</v>
+        <v>0.3260018655523821</v>
       </c>
       <c r="BF141" s="3" t="n">
         <v>0.1109332606816142</v>
@@ -28696,7 +28712,7 @@
         <v>0.6489911174521981</v>
       </c>
       <c r="AM142" s="3" t="n">
-        <v>1.400895737547891</v>
+        <v>1.028569913798749</v>
       </c>
       <c r="AN142" s="3" t="n">
         <v>-0.1905298350617073</v>
@@ -28750,7 +28766,7 @@
         <v>0.849835934551046</v>
       </c>
       <c r="BE142" s="3" t="n">
-        <v>0.3772168609311518</v>
+        <v>0.4233869625556574</v>
       </c>
       <c r="BF142" s="3" t="n">
         <v>0.1142040985569724</v>
@@ -28929,7 +28945,7 @@
         <v>0.8538255195045914</v>
       </c>
       <c r="BE143" s="3" t="n">
-        <v>0.3377455180939549</v>
+        <v>0.3953126249006313</v>
       </c>
       <c r="BF143" s="3" t="n">
         <v>0.1132495989608218</v>
@@ -29068,7 +29084,7 @@
         <v>0.1806327540794069</v>
       </c>
       <c r="AM144" s="3" t="n">
-        <v>1.631807279596769</v>
+        <v>0.8383849051842814</v>
       </c>
       <c r="AN144" s="3" t="n">
         <v>-0.07797842327884785</v>
@@ -29122,7 +29138,7 @@
         <v>0.8612287302428766</v>
       </c>
       <c r="BE144" s="3" t="n">
-        <v>0.04030426927653319</v>
+        <v>0.06147047702532103</v>
       </c>
       <c r="BF144" s="3" t="n">
         <v>0.09422545368711412</v>
@@ -29271,7 +29287,7 @@
         <v>0.1240947582864958</v>
       </c>
       <c r="AM145" s="3" t="n">
-        <v>1.672548173329165</v>
+        <v>0.8124016912561887</v>
       </c>
       <c r="AN145" s="3" t="n">
         <v>-0.07127775772297507</v>
@@ -29325,7 +29341,7 @@
         <v>0.8610146122132175</v>
       </c>
       <c r="BE145" s="3" t="n">
-        <v>0.007111609261670174</v>
+        <v>0.01176648345309374</v>
       </c>
       <c r="BF145" s="3" t="n">
         <v>0.08586368618854456</v>
@@ -29474,7 +29490,7 @@
         <v>0.04999933784548218</v>
       </c>
       <c r="AM146" s="3" t="n">
-        <v>1.769675270965933</v>
+        <v>0.6337263983548209</v>
       </c>
       <c r="AN146" s="3" t="n">
         <v>-0.05042207898854156</v>
@@ -29528,7 +29544,7 @@
         <v>0.8502041923586888</v>
       </c>
       <c r="BE146" s="3" t="n">
-        <v>-0.1143971874897276</v>
+        <v>-0.225900197633875</v>
       </c>
       <c r="BF146" s="3" t="n">
         <v>0.06272700552122121</v>
@@ -29677,7 +29693,7 @@
         <v>0.649744936763909</v>
       </c>
       <c r="AM147" s="3" t="n">
-        <v>1.420719045300522</v>
+        <v>1.301971394154996</v>
       </c>
       <c r="AN147" s="3" t="n">
         <v>-0.1720300379611635</v>
@@ -29731,7 +29747,7 @@
         <v>0.8524492575215106</v>
       </c>
       <c r="BE147" s="3" t="n">
-        <v>0.6072904632065055</v>
+        <v>0.6776268904853171</v>
       </c>
       <c r="BF147" s="3" t="n">
         <v>0.115001958708702</v>
@@ -29880,7 +29896,7 @@
         <v>0.6579198768483105</v>
       </c>
       <c r="AM148" s="3" t="n">
-        <v>1.45233355206932</v>
+        <v>1.264833629437353</v>
       </c>
       <c r="AN148" s="3" t="n">
         <v>-0.13746287630785</v>
@@ -29934,7 +29950,7 @@
         <v>0.858429627103923</v>
       </c>
       <c r="BE148" s="3" t="n">
-        <v>0.5435561025521937</v>
+        <v>0.6073982915566174</v>
       </c>
       <c r="BF148" s="3" t="n">
         <v>0.119046565046569</v>
@@ -30113,7 +30129,7 @@
         <v>0.862275368023569</v>
       </c>
       <c r="BE149" s="3" t="n">
-        <v>0.5987942456615417</v>
+        <v>0.7424631044316846</v>
       </c>
       <c r="BF149" s="3" t="n">
         <v>0.1131182872370901</v>
@@ -30252,7 +30268,7 @@
         <v>0.2086416882240942</v>
       </c>
       <c r="AM150" s="3" t="n">
-        <v>1.614326536615244</v>
+        <v>1.462898158990682</v>
       </c>
       <c r="AN150" s="3" t="n">
         <v>-0.08205185765678846</v>
@@ -30306,7 +30322,7 @@
         <v>0.8640683711233682</v>
       </c>
       <c r="BE150" s="3" t="n">
-        <v>0.471185672463753</v>
+        <v>0.6967608195114541</v>
       </c>
       <c r="BF150" s="3" t="n">
         <v>0.09881331262795938</v>
@@ -30455,7 +30471,7 @@
         <v>0.9694569428991459</v>
       </c>
       <c r="AM151" s="3" t="n">
-        <v>1.104819660937485</v>
+        <v>0.6431616947208306</v>
       </c>
       <c r="AN151" s="3" t="n">
         <v>-0.4556107952799974</v>
@@ -30509,7 +30525,7 @@
         <v>0.8232378252321255</v>
       </c>
       <c r="BE151" s="3" t="n">
-        <v>0.3178002859378126</v>
+        <v>0.3185572618920869</v>
       </c>
       <c r="BF151" s="3" t="n">
         <v>0.1047463316039347</v>
@@ -30688,7 +30704,7 @@
         <v>0.8401802134900317</v>
       </c>
       <c r="BE152" s="3" t="n">
-        <v>0.3347079342697365</v>
+        <v>0.380505594649822</v>
       </c>
       <c r="BF152" s="3" t="n">
         <v>0.1081470649960655</v>
@@ -30827,7 +30843,7 @@
         <v>0.1647323838419266</v>
       </c>
       <c r="AM153" s="3" t="n">
-        <v>1.647629963630205</v>
+        <v>0.9857468379210246</v>
       </c>
       <c r="AN153" s="3" t="n">
         <v>-0.06963824711078981</v>
@@ -30881,7 +30897,7 @@
         <v>0.8457719472300137</v>
       </c>
       <c r="BE153" s="3" t="n">
-        <v>0.125664962991269</v>
+        <v>0.1967509796613171</v>
       </c>
       <c r="BF153" s="3" t="n">
         <v>0.08428232666611862</v>
@@ -31030,7 +31046,7 @@
         <v>0.02167462000612329</v>
       </c>
       <c r="AM154" s="3" t="n">
-        <v>1.844582189414824</v>
+        <v>-0.2646813353784943</v>
       </c>
       <c r="AN154" s="3" t="n">
         <v>-0.03383674043580698</v>
@@ -31084,7 +31100,7 @@
         <v>0.8380040138189584</v>
       </c>
       <c r="BE154" s="3" t="n">
-        <v>-0.5119990967744711</v>
+        <v>-1.170054059868003</v>
       </c>
       <c r="BF154" s="3" t="n">
         <v>0.04233530501091616</v>
@@ -31233,7 +31249,7 @@
         <v>0.1140510487946486</v>
       </c>
       <c r="AM155" s="3" t="n">
-        <v>1.685766047216368</v>
+        <v>0.5619916077094881</v>
       </c>
       <c r="AN155" s="3" t="n">
         <v>-0.0642590884487706</v>
@@ -31287,7 +31303,7 @@
         <v>0.8452754900121209</v>
       </c>
       <c r="BE155" s="3" t="n">
-        <v>-0.24873759103412</v>
+        <v>-0.2487618716743106</v>
       </c>
       <c r="BF155" s="3" t="n">
         <v>0.076300596111884</v>
@@ -31466,7 +31482,7 @@
         <v>0.8317786627170617</v>
       </c>
       <c r="BE156" s="3" t="n">
-        <v>0.3879016900103311</v>
+        <v>0.3878771587007718</v>
       </c>
       <c r="BF156" s="3" t="n">
         <v>0.1069602061655732</v>
@@ -31605,7 +31621,7 @@
         <v>0.9041449738313518</v>
       </c>
       <c r="AM157" s="3" t="n">
-        <v>1.219258539535372</v>
+        <v>0.7057590234316403</v>
       </c>
       <c r="AN157" s="3" t="n">
         <v>-0.3462879174625233</v>
@@ -31659,7 +31675,7 @@
         <v>0.82872647170098</v>
       </c>
       <c r="BE157" s="3" t="n">
-        <v>0.2630250081207566</v>
+        <v>0.269273712395216</v>
       </c>
       <c r="BF157" s="3" t="n">
         <v>0.1070446164428513</v>
@@ -31838,7 +31854,7 @@
         <v>0.8404592273918582</v>
       </c>
       <c r="BE158" s="3" t="n">
-        <v>0.1955195035625874</v>
+        <v>0.223882976389617</v>
       </c>
       <c r="BF158" s="3" t="n">
         <v>0.1074754143414465</v>
@@ -31977,7 +31993,7 @@
         <v>0.2732882283862142</v>
       </c>
       <c r="AM159" s="3" t="n">
-        <v>1.598800796180186</v>
+        <v>0.856300505645309</v>
       </c>
       <c r="AN159" s="3" t="n">
         <v>-0.07149203906192791</v>
@@ -32031,7 +32047,7 @@
         <v>0.8464674277053329</v>
       </c>
       <c r="BE159" s="3" t="n">
-        <v>0.06647229834548347</v>
+        <v>0.09264612708617996</v>
       </c>
       <c r="BF159" s="3" t="n">
         <v>0.09567239861110122</v>
@@ -32180,7 +32196,7 @@
         <v>0.1038091246867855</v>
       </c>
       <c r="AM160" s="3" t="n">
-        <v>1.696997505184316</v>
+        <v>0.4634858623064511</v>
       </c>
       <c r="AN160" s="3" t="n">
         <v>-0.06198562367742688</v>
@@ -32234,7 +32250,7 @@
         <v>0.8429558951018732</v>
       </c>
       <c r="BE160" s="3" t="n">
-        <v>-0.205974760488724</v>
+        <v>-0.3540200784469937</v>
       </c>
       <c r="BF160" s="3" t="n">
         <v>0.0729067998313752</v>
@@ -32413,7 +32429,7 @@
         <v>0.8197787912430065</v>
       </c>
       <c r="BE161" s="3" t="n">
-        <v>0.2937658415773666</v>
+        <v>0.291800088988185</v>
       </c>
       <c r="BF161" s="3" t="n">
         <v>0.1030436980927747</v>
@@ -32552,7 +32568,7 @@
         <v>0.3134207606333207</v>
       </c>
       <c r="AM162" s="3" t="n">
-        <v>1.589227192504068</v>
+        <v>0.903502786017134</v>
       </c>
       <c r="AN162" s="3" t="n">
         <v>-0.06865316777548924</v>
@@ -32606,7 +32622,7 @@
         <v>0.8473043961136094</v>
       </c>
       <c r="BE162" s="3" t="n">
-        <v>0.1059221134205062</v>
+        <v>0.1432157736528446</v>
       </c>
       <c r="BF162" s="3" t="n">
         <v>0.09879185983362347</v>
@@ -32785,7 +32801,7 @@
         <v>0.8390133885867989</v>
       </c>
       <c r="BE163" s="3" t="n">
-        <v>0.2472363449705373</v>
+        <v>0.2776412974303627</v>
       </c>
       <c r="BF163" s="3" t="n">
         <v>0.1079885992214</v>
@@ -32924,7 +32940,7 @@
         <v>0.2000853229246337</v>
       </c>
       <c r="AM164" s="3" t="n">
-        <v>1.629583116386512</v>
+        <v>0.8565296371267855</v>
       </c>
       <c r="AN164" s="3" t="n">
         <v>-0.07025902105047499</v>
@@ -32978,7 +32994,7 @@
         <v>0.8425647894035259</v>
       </c>
       <c r="BE164" s="3" t="n">
-        <v>0.0515095092243558</v>
+        <v>0.07686758945876705</v>
       </c>
       <c r="BF164" s="3" t="n">
         <v>0.08656618184334672</v>
@@ -33127,7 +33143,7 @@
         <v>0.08452767349194834</v>
       </c>
       <c r="AM165" s="3" t="n">
-        <v>1.716787437527125</v>
+        <v>0.488074418678932</v>
       </c>
       <c r="AN165" s="3" t="n">
         <v>-0.05984159054561033</v>
@@ -33181,7 +33197,7 @@
         <v>0.8485820036869653</v>
       </c>
       <c r="BE165" s="3" t="n">
-        <v>-0.1903093440177043</v>
+        <v>-0.3403985048118253</v>
       </c>
       <c r="BF165" s="3" t="n">
         <v>0.07180906905298159</v>
@@ -33330,7 +33346,7 @@
         <v>0.02447381856465209</v>
       </c>
       <c r="AM166" s="3" t="n">
-        <v>1.833784401586423</v>
+        <v>-0.6018963736017289</v>
       </c>
       <c r="AN166" s="3" t="n">
         <v>-0.03676462289095872</v>
@@ -33384,7 +33400,7 @@
         <v>0.8444404448013485</v>
       </c>
       <c r="BE166" s="3" t="n">
-        <v>-0.6725623173334841</v>
+        <v>-1.500406262949461</v>
       </c>
       <c r="BF166" s="3" t="n">
         <v>0.04818013200026509</v>
@@ -33533,7 +33549,7 @@
         <v>0.02374271764684645</v>
       </c>
       <c r="AM167" s="3" t="n">
-        <v>1.827313259636109</v>
+        <v>-1.684744344365288</v>
       </c>
       <c r="AN167" s="3" t="n">
         <v>-0.01258966795551419</v>
@@ -33587,7 +33603,7 @@
         <v>0.3047693078580407</v>
       </c>
       <c r="BE167" s="3" t="n">
-        <v>-1.155694841707516</v>
+        <v>-2.592106140205586</v>
       </c>
       <c r="BF167" s="3" t="n">
         <v>-0.2680286882292236</v>
@@ -33736,7 +33752,7 @@
         <v>0.6640230044391858</v>
       </c>
       <c r="AM168" s="3" t="n">
-        <v>1.340920738067103</v>
+        <v>1.25911424925931</v>
       </c>
       <c r="AN168" s="3" t="n">
         <v>-0.2496275865129224</v>
@@ -33790,7 +33806,7 @@
         <v>0.8456200724330498</v>
       </c>
       <c r="BE168" s="3" t="n">
-        <v>0.6413564929445565</v>
+        <v>0.7134676734822195</v>
       </c>
       <c r="BF168" s="3" t="n">
         <v>0.1120700495405709</v>
@@ -33939,7 +33955,7 @@
         <v>0.1548977839717105</v>
       </c>
       <c r="AM169" s="3" t="n">
-        <v>1.649218523271327</v>
+        <v>1.252945398690635</v>
       </c>
       <c r="AN169" s="3" t="n">
         <v>-0.07461610583089817</v>
@@ -33993,7 +34009,7 @@
         <v>0.8595624184817781</v>
       </c>
       <c r="BE169" s="3" t="n">
-        <v>0.2936553595573054</v>
+        <v>0.4656441899704207</v>
       </c>
       <c r="BF169" s="3" t="n">
         <v>0.09003779243573307</v>
@@ -34142,7 +34158,7 @@
         <v>0.05888720528251395</v>
       </c>
       <c r="AM170" s="3" t="n">
-        <v>1.752699229867674</v>
+        <v>1.074964185261263</v>
       </c>
       <c r="AN170" s="3" t="n">
         <v>-0.0542077557939119</v>
@@ -34196,7 +34212,7 @@
         <v>0.8530910812179451</v>
       </c>
       <c r="BE170" s="3" t="n">
-        <v>0.1168993011287451</v>
+        <v>0.2257184482243819</v>
       </c>
       <c r="BF170" s="3" t="n">
         <v>0.06732766808787237</v>
@@ -34345,7 +34361,7 @@
         <v>0.8129702022769218</v>
       </c>
       <c r="AM171" s="3" t="n">
-        <v>1.374646764355409</v>
+        <v>1.251783795436786</v>
       </c>
       <c r="AN171" s="3" t="n">
         <v>-0.1996137847836088</v>
@@ -34399,7 +34415,7 @@
         <v>0.8417072674150483</v>
       </c>
       <c r="BE171" s="3" t="n">
-        <v>0.6320064641463439</v>
+        <v>0.6642673056508858</v>
       </c>
       <c r="BF171" s="3" t="n">
         <v>0.1125181732730702</v>
@@ -34548,7 +34564,7 @@
         <v>0.6095071155689398</v>
       </c>
       <c r="AM172" s="3" t="n">
-        <v>1.440362166162277</v>
+        <v>1.251192778969079</v>
       </c>
       <c r="AN172" s="3" t="n">
         <v>-0.1559147248074553</v>
@@ -34602,7 +34618,7 @@
         <v>0.8556667432343965</v>
       </c>
       <c r="BE172" s="3" t="n">
-        <v>0.5310113411957482</v>
+        <v>0.6089690582916683</v>
       </c>
       <c r="BF172" s="3" t="n">
         <v>0.1163748057267599</v>
@@ -34751,7 +34767,7 @@
         <v>0.5338154867077518</v>
       </c>
       <c r="AM173" s="3" t="n">
-        <v>1.43810571270596</v>
+        <v>1.214611667346308</v>
       </c>
       <c r="AN173" s="3" t="n">
         <v>-0.1713998984582016</v>
@@ -34805,7 +34821,7 @@
         <v>0.8581658585302514</v>
       </c>
       <c r="BE173" s="3" t="n">
-        <v>0.490992018165763</v>
+        <v>0.5812587602224288</v>
       </c>
       <c r="BF173" s="3" t="n">
         <v>0.1149248874660726</v>
@@ -34954,7 +34970,7 @@
         <v>0.14427214524429</v>
       </c>
       <c r="AM174" s="3" t="n">
-        <v>1.655027482362718</v>
+        <v>1.217407662042399</v>
       </c>
       <c r="AN174" s="3" t="n">
         <v>-0.07485106488814941</v>
@@ -35008,7 +35024,7 @@
         <v>0.8619378396214666</v>
       </c>
       <c r="BE174" s="3" t="n">
-        <v>0.2649891128275752</v>
+        <v>0.4273194533051149</v>
       </c>
       <c r="BF174" s="3" t="n">
         <v>0.08986987875744228</v>
@@ -35157,7 +35173,7 @@
         <v>0.06387752326043633</v>
       </c>
       <c r="AM175" s="3" t="n">
-        <v>1.744507960631185</v>
+        <v>1.366870873183099</v>
       </c>
       <c r="AN175" s="3" t="n">
         <v>-0.05617366783803368</v>
@@ -35211,7 +35227,7 @@
         <v>0.8547613604043748</v>
       </c>
       <c r="BE175" s="3" t="n">
-        <v>0.2758633103891025</v>
+        <v>0.5227037267865234</v>
       </c>
       <c r="BF175" s="3" t="n">
         <v>0.06954478396393486</v>
@@ -35360,7 +35376,7 @@
         <v>0.7173366150620142</v>
       </c>
       <c r="AM176" s="3" t="n">
-        <v>1.37237363192975</v>
+        <v>1.202123163676941</v>
       </c>
       <c r="AN176" s="3" t="n">
         <v>-0.2118896451345467</v>
@@ -35414,7 +35430,7 @@
         <v>0.8449965868473616</v>
       </c>
       <c r="BE176" s="3" t="n">
-        <v>0.5712283622152032</v>
+        <v>0.6218811702793396</v>
       </c>
       <c r="BF176" s="3" t="n">
         <v>0.1126775794102814</v>
@@ -35563,7 +35579,7 @@
         <v>0.5751674625856931</v>
       </c>
       <c r="AM177" s="3" t="n">
-        <v>1.374695224176391</v>
+        <v>1.164392939156224</v>
       </c>
       <c r="AN177" s="3" t="n">
         <v>-0.2275714947008632</v>
@@ -35617,7 +35633,7 @@
         <v>0.8517606617431928</v>
       </c>
       <c r="BE177" s="3" t="n">
-        <v>0.5100842524325897</v>
+        <v>0.5908310744184599</v>
       </c>
       <c r="BF177" s="3" t="n">
         <v>0.1131866889896381</v>
@@ -35796,7 +35812,7 @@
         <v>0.8596526275464277</v>
       </c>
       <c r="BE178" s="3" t="n">
-        <v>0.4809903360600606</v>
+        <v>0.5918870121053984</v>
       </c>
       <c r="BF178" s="3" t="n">
         <v>0.113074205142747</v>
@@ -35935,7 +35951,7 @@
         <v>0.06982252138384884</v>
       </c>
       <c r="AM179" s="3" t="n">
-        <v>1.736308289714346</v>
+        <v>1.636275438836335</v>
       </c>
       <c r="AN179" s="3" t="n">
         <v>-0.05697452023708605</v>
@@ -35989,7 +36005,7 @@
         <v>0.8511942628752543</v>
       </c>
       <c r="BE179" s="3" t="n">
-        <v>0.4276566850025175</v>
+        <v>0.7966085540977051</v>
       </c>
       <c r="BF179" s="3" t="n">
         <v>0.06945814071976694</v>
@@ -36138,7 +36154,7 @@
         <v>0.5456729434048265</v>
       </c>
       <c r="AM180" s="3" t="n">
-        <v>1.447305253283292</v>
+        <v>1.313391350253939</v>
       </c>
       <c r="AN180" s="3" t="n">
         <v>-0.1582415527032568</v>
@@ -36192,7 +36208,7 @@
         <v>0.8575082776930549</v>
       </c>
       <c r="BE180" s="3" t="n">
-        <v>0.5686670239794743</v>
+        <v>0.668859499963921</v>
       </c>
       <c r="BF180" s="3" t="n">
         <v>0.1157486986563563</v>
@@ -36341,7 +36357,7 @@
         <v>0.482079309835857</v>
       </c>
       <c r="AM181" s="3" t="n">
-        <v>1.477684094211953</v>
+        <v>1.360650977848083</v>
       </c>
       <c r="AN181" s="3" t="n">
         <v>-0.1393267962592679</v>
@@ -36395,7 +36411,7 @@
         <v>0.8629392138223503</v>
       </c>
       <c r="BE181" s="3" t="n">
-        <v>0.5697953772645487</v>
+        <v>0.6914723288717405</v>
       </c>
       <c r="BF181" s="3" t="n">
         <v>0.1161027525010545</v>
@@ -36544,7 +36560,7 @@
         <v>0.2684482346674679</v>
       </c>
       <c r="AM182" s="3" t="n">
-        <v>1.592111182808494</v>
+        <v>1.463716091581144</v>
       </c>
       <c r="AN182" s="3" t="n">
         <v>-0.08054308326083459</v>
@@ -36598,7 +36614,7 @@
         <v>0.8617131586245169</v>
       </c>
       <c r="BE182" s="3" t="n">
-        <v>0.5076570575826442</v>
+        <v>0.7079320418073141</v>
       </c>
       <c r="BF182" s="3" t="n">
         <v>0.1030944592580686</v>
@@ -36747,7 +36763,7 @@
         <v>0.0974296901400605</v>
       </c>
       <c r="AM183" s="3" t="n">
-        <v>1.701357907144472</v>
+        <v>1.400791214215855</v>
       </c>
       <c r="AN183" s="3" t="n">
         <v>-0.0637130716853469</v>
@@ -36801,7 +36817,7 @@
         <v>0.8529760327213735</v>
       </c>
       <c r="BE183" s="3" t="n">
-        <v>0.3344770530293943</v>
+        <v>0.5819687964862924</v>
       </c>
       <c r="BF183" s="3" t="n">
         <v>0.07688422046302344</v>
@@ -36950,7 +36966,7 @@
         <v>0.9175595667223198</v>
       </c>
       <c r="AM184" s="3" t="n">
-        <v>1.373576778401399</v>
+        <v>1.246570896380939</v>
       </c>
       <c r="AN184" s="3" t="n">
         <v>-0.1912943365369151</v>
@@ -37004,7 +37020,7 @@
         <v>0.8384968522800954</v>
       </c>
       <c r="BE184" s="3" t="n">
-        <v>0.6459688517113917</v>
+        <v>0.6554296754486966</v>
       </c>
       <c r="BF184" s="3" t="n">
         <v>0.1122118175382203</v>
@@ -37153,7 +37169,7 @@
         <v>0.6399065264335726</v>
       </c>
       <c r="AM185" s="3" t="n">
-        <v>1.403969251914764</v>
+        <v>1.332537857916121</v>
       </c>
       <c r="AN185" s="3" t="n">
         <v>-0.1894436667335391</v>
@@ -37207,7 +37223,7 @@
         <v>0.8506315419825285</v>
       </c>
       <c r="BE185" s="3" t="n">
-        <v>0.6439752790655343</v>
+        <v>0.7252750653255081</v>
       </c>
       <c r="BF185" s="3" t="n">
         <v>0.1141047829121065</v>
@@ -37386,7 +37402,7 @@
         <v>0.8564887757167932</v>
       </c>
       <c r="BE186" s="3" t="n">
-        <v>0.6132523170673955</v>
+        <v>0.7376521810669034</v>
       </c>
       <c r="BF186" s="3" t="n">
         <v>0.113152767734129</v>
@@ -37525,7 +37541,7 @@
         <v>0.3379822185620592</v>
       </c>
       <c r="AM187" s="3" t="n">
-        <v>1.580249468841842</v>
+        <v>1.630579294499473</v>
       </c>
       <c r="AN187" s="3" t="n">
         <v>-0.0706108406329552</v>
@@ -37579,7 +37595,7 @@
         <v>0.8637008043980637</v>
       </c>
       <c r="BE187" s="3" t="n">
-        <v>0.6625000194765271</v>
+        <v>0.87575998039503</v>
       </c>
       <c r="BF187" s="3" t="n">
         <v>0.1090493482482088</v>
@@ -37728,7 +37744,7 @@
         <v>0.1014507847204887</v>
       </c>
       <c r="AM188" s="3" t="n">
-        <v>1.696259635559572</v>
+        <v>1.795348193260222</v>
       </c>
       <c r="AN188" s="3" t="n">
         <v>-0.06561286531005472</v>
@@ -37782,7 +37798,7 @@
         <v>0.8564192125727179</v>
       </c>
       <c r="BE188" s="3" t="n">
-        <v>0.5679611095672841</v>
+        <v>0.980024808135463</v>
       </c>
       <c r="BF188" s="3" t="n">
         <v>0.07947021831395826</v>
@@ -37931,7 +37947,7 @@
         <v>0.6382980043854865</v>
       </c>
       <c r="AM189" s="3" t="n">
-        <v>1.397533228143142</v>
+        <v>1.372082451825592</v>
       </c>
       <c r="AN189" s="3" t="n">
         <v>-0.1963977767595696</v>
@@ -37985,7 +38001,7 @@
         <v>0.8502384427859474</v>
       </c>
       <c r="BE189" s="3" t="n">
-        <v>0.6865748927905149</v>
+        <v>0.7715147261338059</v>
       </c>
       <c r="BF189" s="3" t="n">
         <v>0.1137475293174074</v>
@@ -38134,7 +38150,7 @@
         <v>0.5580265221579953</v>
       </c>
       <c r="AM190" s="3" t="n">
-        <v>1.446149781103848</v>
+        <v>1.269693923607218</v>
       </c>
       <c r="AN190" s="3" t="n">
         <v>-0.1596916735696049</v>
@@ -38188,7 +38204,7 @@
         <v>0.8581740506545775</v>
       </c>
       <c r="BE190" s="3" t="n">
-        <v>0.5387590352522214</v>
+        <v>0.6264648698400962</v>
       </c>
       <c r="BF190" s="3" t="n">
         <v>0.1156311518066719</v>
@@ -38337,7 +38353,7 @@
         <v>0.2623975967447766</v>
       </c>
       <c r="AM191" s="3" t="n">
-        <v>1.595673251607801</v>
+        <v>1.400217321126115</v>
       </c>
       <c r="AN191" s="3" t="n">
         <v>-0.07916839245479568</v>
@@ -38391,7 +38407,7 @@
         <v>0.8599198443222136</v>
       </c>
       <c r="BE191" s="3" t="n">
-        <v>0.4579273365773064</v>
+        <v>0.6419648915496126</v>
       </c>
       <c r="BF191" s="3" t="n">
         <v>0.1017123575900569</v>
@@ -38540,7 +38556,7 @@
         <v>0.09050585127981897</v>
       </c>
       <c r="AM192" s="3" t="n">
-        <v>1.708689687346496</v>
+        <v>1.378756221468675</v>
       </c>
       <c r="AN192" s="3" t="n">
         <v>-0.06274071353716693</v>
@@ -38594,7 +38610,7 @@
         <v>0.8545537856579535</v>
       </c>
       <c r="BE192" s="3" t="n">
-        <v>0.314838261170113</v>
+        <v>0.5557817345640103</v>
       </c>
       <c r="BF192" s="3" t="n">
         <v>0.0759991928317006</v>
@@ -38743,7 +38759,7 @@
         <v>0.6168587506216229</v>
       </c>
       <c r="AM193" s="3" t="n">
-        <v>1.382138247166307</v>
+        <v>1.345769264395746</v>
       </c>
       <c r="AN193" s="3" t="n">
         <v>-0.2145421434772181</v>
@@ -38797,7 +38813,7 @@
         <v>0.8501288087652525</v>
       </c>
       <c r="BE193" s="3" t="n">
-        <v>0.6714629740016561</v>
+        <v>0.7619712125512021</v>
       </c>
       <c r="BF193" s="3" t="n">
         <v>0.1132033272193036</v>
@@ -38946,7 +38962,7 @@
         <v>0.653863523272169</v>
       </c>
       <c r="AM194" s="3" t="n">
-        <v>1.443057855847317</v>
+        <v>1.273530087693069</v>
       </c>
       <c r="AN194" s="3" t="n">
         <v>-0.1469924931248</v>
@@ -39000,7 +39016,7 @@
         <v>0.8556505610827412</v>
       </c>
       <c r="BE194" s="3" t="n">
-        <v>0.557401210644616</v>
+        <v>0.6254974063318107</v>
       </c>
       <c r="BF194" s="3" t="n">
         <v>0.1176488758445104</v>
@@ -39149,7 +39165,7 @@
         <v>0.5382627971286424</v>
       </c>
       <c r="AM195" s="3" t="n">
-        <v>1.432362574525349</v>
+        <v>1.236195086462758</v>
       </c>
       <c r="AN195" s="3" t="n">
         <v>-0.1765823457057587</v>
@@ -39203,7 +39219,7 @@
         <v>0.8575417221567018</v>
       </c>
       <c r="BE195" s="3" t="n">
-        <v>0.5161357188591461</v>
+        <v>0.608304972052963</v>
       </c>
       <c r="BF195" s="3" t="n">
         <v>0.1147071187395814</v>
@@ -39352,7 +39368,7 @@
         <v>0.2444841730788833</v>
       </c>
       <c r="AM196" s="3" t="n">
-        <v>1.600079373988336</v>
+        <v>1.302062559729619</v>
       </c>
       <c r="AN196" s="3" t="n">
         <v>-0.08139802644836014</v>
@@ -39406,7 +39422,7 @@
         <v>0.8621501226107222</v>
       </c>
       <c r="BE196" s="3" t="n">
-        <v>0.3787877898749585</v>
+        <v>0.5427218859596313</v>
       </c>
       <c r="BF196" s="3" t="n">
         <v>0.1012648650234328</v>
@@ -39555,7 +39571,7 @@
         <v>0.0822965879812998</v>
       </c>
       <c r="AM197" s="3" t="n">
-        <v>1.718126716202709</v>
+        <v>1.075976969460146</v>
       </c>
       <c r="AN197" s="3" t="n">
         <v>-0.0613921882238907</v>
@@ -39609,7 +39625,7 @@
         <v>0.8559701035240495</v>
       </c>
       <c r="BE197" s="3" t="n">
-        <v>0.1370160760120932</v>
+        <v>0.2476097054707368</v>
       </c>
       <c r="BF197" s="3" t="n">
         <v>0.07501477336816181</v>
@@ -39758,7 +39774,7 @@
         <v>0.02313929963903122</v>
       </c>
       <c r="AM198" s="3" t="n">
-        <v>1.824606416112405</v>
+        <v>0.4031883658204553</v>
       </c>
       <c r="AN198" s="3" t="n">
         <v>0.001608792586350494</v>
@@ -39812,7 +39828,7 @@
         <v>0.1640973856346188</v>
       </c>
       <c r="BE198" s="3" t="n">
-        <v>-0.2238705565967379</v>
+        <v>-0.5099192385289226</v>
       </c>
       <c r="BF198" s="3" t="n">
         <v>-0.36222726733954</v>
@@ -39961,7 +39977,7 @@
         <v>0.7782179040211995</v>
       </c>
       <c r="AM199" s="3" t="n">
-        <v>1.377175137410876</v>
+        <v>1.235118424305357</v>
       </c>
       <c r="AN199" s="3" t="n">
         <v>-0.2001485271135776</v>
@@ -40015,7 +40031,7 @@
         <v>0.8430430892386326</v>
       </c>
       <c r="BE199" s="3" t="n">
-        <v>0.6073704695870341</v>
+        <v>0.6466051191567078</v>
       </c>
       <c r="BF199" s="3" t="n">
         <v>0.1129197557546622</v>
@@ -40164,7 +40180,7 @@
         <v>0.5746204823134636</v>
       </c>
       <c r="AM200" s="3" t="n">
-        <v>1.374891557136648</v>
+        <v>1.263681943098342</v>
       </c>
       <c r="AN200" s="3" t="n">
         <v>-0.227528623091053</v>
@@ -40218,7 +40234,7 @@
         <v>0.8518393335550594</v>
       </c>
       <c r="BE200" s="3" t="n">
-        <v>0.5953756844022503</v>
+        <v>0.6900004760755446</v>
       </c>
       <c r="BF200" s="3" t="n">
         <v>0.1131902258118309</v>
@@ -40367,7 +40383,7 @@
         <v>0.5190885031485019</v>
       </c>
       <c r="AM201" s="3" t="n">
-        <v>1.419066640212471</v>
+        <v>1.31146058821558</v>
       </c>
       <c r="AN201" s="3" t="n">
         <v>-0.1913112699092296</v>
@@ -40421,7 +40437,7 @@
         <v>0.8567193141547769</v>
       </c>
       <c r="BE201" s="3" t="n">
-        <v>0.5843277357978195</v>
+        <v>0.6975829030639593</v>
       </c>
       <c r="BF201" s="3" t="n">
         <v>0.1142380933332082</v>
@@ -40570,7 +40586,7 @@
         <v>0.3101295495695485</v>
       </c>
       <c r="AM202" s="3" t="n">
-        <v>1.580963435553784</v>
+        <v>1.413338186215543</v>
       </c>
       <c r="AN202" s="3" t="n">
         <v>-0.07806993791312422</v>
@@ -40624,7 +40640,7 @@
         <v>0.8631515492253832</v>
       </c>
       <c r="BE202" s="3" t="n">
-        <v>0.4897001315826186</v>
+        <v>0.6618914373952137</v>
       </c>
       <c r="BF202" s="3" t="n">
         <v>0.106923083267476</v>
@@ -40773,7 +40789,7 @@
         <v>0.1355625055354125</v>
       </c>
       <c r="AM203" s="3" t="n">
-        <v>1.664339506267196</v>
+        <v>1.294936368488005</v>
       </c>
       <c r="AN203" s="3" t="n">
         <v>-0.07161869381855734</v>
@@ -40827,7 +40843,7 @@
         <v>0.8581275199996395</v>
       </c>
       <c r="BE203" s="3" t="n">
-        <v>0.3057207331362674</v>
+        <v>0.4985759622636861</v>
       </c>
       <c r="BF203" s="3" t="n">
         <v>0.08640114643893075</v>
@@ -40976,7 +40992,7 @@
         <v>0.02411223802431175</v>
       </c>
       <c r="AM204" s="3" t="n">
-        <v>1.835293986212097</v>
+        <v>1.103588487687155</v>
       </c>
       <c r="AN204" s="3" t="n">
         <v>-0.03654283150289839</v>
@@ -41030,7 +41046,7 @@
         <v>0.8449530250064098</v>
       </c>
       <c r="BE204" s="3" t="n">
-        <v>0.09065727487558026</v>
+        <v>0.2042129103325557</v>
       </c>
       <c r="BF204" s="3" t="n">
         <v>0.04803532529145259</v>
@@ -41179,7 +41195,7 @@
         <v>0.5948184460829606</v>
       </c>
       <c r="AM205" s="3" t="n">
-        <v>1.377363410125727</v>
+        <v>1.284536479486802</v>
       </c>
       <c r="AN205" s="3" t="n">
         <v>-0.222342538815813</v>
@@ -41233,7 +41249,7 @@
         <v>0.8509543322517745</v>
       </c>
       <c r="BE205" s="3" t="n">
-        <v>0.6170852174022728</v>
+        <v>0.7070260438318453</v>
       </c>
       <c r="BF205" s="3" t="n">
         <v>0.1131064037341478</v>
@@ -41382,7 +41398,7 @@
         <v>0.5243494268062803</v>
       </c>
       <c r="AM206" s="3" t="n">
-        <v>1.452617753491116</v>
+        <v>1.331112656649925</v>
       </c>
       <c r="AN206" s="3" t="n">
         <v>-0.1579270316773531</v>
@@ -41436,7 +41452,7 @@
         <v>0.859635912272822</v>
       </c>
       <c r="BE206" s="3" t="n">
-        <v>0.5760430243976938</v>
+        <v>0.6837672957430434</v>
       </c>
       <c r="BF206" s="3" t="n">
         <v>0.1155264076971648</v>
@@ -41585,7 +41601,7 @@
         <v>0.2873860446666595</v>
       </c>
       <c r="AM207" s="3" t="n">
-        <v>1.584408825990334</v>
+        <v>1.550961035696231</v>
       </c>
       <c r="AN207" s="3" t="n">
         <v>-0.08189767161417794</v>
@@ -41639,7 +41655,7 @@
         <v>0.8637679904973594</v>
       </c>
       <c r="BE207" s="3" t="n">
-        <v>0.5815553452769455</v>
+        <v>0.7997054585081533</v>
       </c>
       <c r="BF207" s="3" t="n">
         <v>0.1056348053835968</v>
@@ -41788,7 +41804,7 @@
         <v>0.8666572289418291</v>
       </c>
       <c r="AM208" s="3" t="n">
-        <v>1.37789866755812</v>
+        <v>1.225446407288133</v>
       </c>
       <c r="AN208" s="3" t="n">
         <v>-0.1911467232657738</v>
@@ -41842,7 +41858,7 @@
         <v>0.8405717924110887</v>
       </c>
       <c r="BE208" s="3" t="n">
-        <v>0.6128244102698194</v>
+        <v>0.6320704351419593</v>
       </c>
       <c r="BF208" s="3" t="n">
         <v>0.1126996384297127</v>
@@ -41991,7 +42007,7 @@
         <v>0.6307571650003917</v>
       </c>
       <c r="AM209" s="3" t="n">
-        <v>1.406630463240018</v>
+        <v>1.281649921132475</v>
       </c>
       <c r="AN209" s="3" t="n">
         <v>-0.1879972818378804</v>
@@ -42045,7 +42061,7 @@
         <v>0.8512706380549444</v>
       </c>
       <c r="BE209" s="3" t="n">
-        <v>0.5953384230106069</v>
+        <v>0.6723333304314068</v>
       </c>
       <c r="BF209" s="3" t="n">
         <v>0.1141913374040165</v>
@@ -42224,7 +42240,7 @@
         <v>0.8560646085486171</v>
       </c>
       <c r="BE210" s="3" t="n">
-        <v>0.5756683281863735</v>
+        <v>0.6884662619208847</v>
       </c>
       <c r="BF210" s="3" t="n">
         <v>0.1132232600861104</v>
@@ -42363,7 +42379,7 @@
         <v>0.3302167956891202</v>
       </c>
       <c r="AM211" s="3" t="n">
-        <v>1.576584363946685</v>
+        <v>1.496005186072437</v>
       </c>
       <c r="AN211" s="3" t="n">
         <v>-0.07678352527379251</v>
@@ -42417,7 +42433,7 @@
         <v>0.8658683073641024</v>
       </c>
       <c r="BE211" s="3" t="n">
-        <v>0.5608012446418092</v>
+        <v>0.7461047667359911</v>
       </c>
       <c r="BF211" s="3" t="n">
         <v>0.1095888298928872</v>
@@ -42566,7 +42582,7 @@
         <v>0.02688395596630731</v>
       </c>
       <c r="AM212" s="3" t="n">
-        <v>1.826996798849365</v>
+        <v>1.742001673556921</v>
       </c>
       <c r="AN212" s="3" t="n">
         <v>-0.03802592963506257</v>
@@ -42620,7 +42636,7 @@
         <v>0.8426397552951462</v>
       </c>
       <c r="BE212" s="3" t="n">
-        <v>0.3848874208228925</v>
+        <v>0.8475162389497701</v>
       </c>
       <c r="BF212" s="3" t="n">
         <v>0.0480325119801183</v>
@@ -42769,7 +42785,7 @@
         <v>0.6148905460843939</v>
       </c>
       <c r="AM213" s="3" t="n">
-        <v>1.376915966178157</v>
+        <v>1.409824666801265</v>
       </c>
       <c r="AN213" s="3" t="n">
         <v>-0.2207255745940014</v>
@@ -42823,7 +42839,7 @@
         <v>0.8502571395809835</v>
       </c>
       <c r="BE213" s="3" t="n">
-        <v>0.7340530258396127</v>
+        <v>0.8317294710091874</v>
       </c>
       <c r="BF213" s="3" t="n">
         <v>0.1129866917559883</v>
@@ -42972,7 +42988,7 @@
         <v>0.1190709790854996</v>
       </c>
       <c r="AM214" s="3" t="n">
-        <v>1.678742513978786</v>
+        <v>1.641071277701347</v>
       </c>
       <c r="AN214" s="3" t="n">
         <v>-0.06860970085896689</v>
@@ -43026,7 +43042,7 @@
         <v>0.8564163231850441</v>
       </c>
       <c r="BE214" s="3" t="n">
-        <v>0.4999772891696511</v>
+        <v>0.8360048711414375</v>
       </c>
       <c r="BF214" s="3" t="n">
         <v>0.08282271470126992</v>
@@ -43175,7 +43191,7 @@
         <v>0.2934880194802195</v>
       </c>
       <c r="AM215" s="3" t="n">
-        <v>1.581774234105073</v>
+        <v>1.515102025064899</v>
       </c>
       <c r="AN215" s="3" t="n">
         <v>-0.08116203480751005</v>
@@ -43229,7 +43245,7 @@
         <v>0.8630710762236153</v>
       </c>
       <c r="BE215" s="3" t="n">
-        <v>0.5594750893995354</v>
+        <v>0.7647959254161172</v>
       </c>
       <c r="BF215" s="3" t="n">
         <v>0.1061356961274463</v>
@@ -43378,7 +43394,7 @@
         <v>0.1540973288294479</v>
       </c>
       <c r="AM216" s="3" t="n">
-        <v>1.649708790256719</v>
+        <v>1.64269158547168</v>
       </c>
       <c r="AN216" s="3" t="n">
         <v>-0.07451433192200319</v>
@@ -43432,7 +43448,7 @@
         <v>0.8597131450715674</v>
       </c>
       <c r="BE216" s="3" t="n">
-        <v>0.5420577508425084</v>
+        <v>0.8550943563043217</v>
       </c>
       <c r="BF216" s="3" t="n">
         <v>0.08988568078608272</v>
@@ -43581,7 +43597,7 @@
         <v>0.3200645930381745</v>
       </c>
       <c r="AM217" s="3" t="n">
-        <v>1.584959666978342</v>
+        <v>1.589122468421388</v>
       </c>
       <c r="AN217" s="3" t="n">
         <v>-0.07150871930401237</v>
@@ -43635,7 +43651,7 @@
         <v>0.8576223788019135</v>
       </c>
       <c r="BE217" s="3" t="n">
-        <v>0.6238768789423312</v>
+        <v>0.8323969945842232</v>
       </c>
       <c r="BF217" s="3" t="n">
         <v>0.1046119862939326</v>
@@ -43784,7 +43800,7 @@
         <v>0.1843500658019832</v>
       </c>
       <c r="AM218" s="3" t="n">
-        <v>1.628640835778457</v>
+        <v>1.639022286628176</v>
       </c>
       <c r="AN218" s="3" t="n">
         <v>-0.07858774632620558</v>
@@ -43838,7 +43854,7 @@
         <v>0.8613125947017214</v>
       </c>
       <c r="BE218" s="3" t="n">
-        <v>0.5674289027861511</v>
+        <v>0.8639957419020499</v>
       </c>
       <c r="BF218" s="3" t="n">
         <v>0.09492512168853841</v>
@@ -43987,7 +44003,7 @@
         <v>0.0431812182117035</v>
       </c>
       <c r="AM219" s="3" t="n">
-        <v>1.784592366533342</v>
+        <v>2.069928383440886</v>
       </c>
       <c r="AN219" s="3" t="n">
         <v>-0.04638034912359679</v>
@@ -44041,7 +44057,7 @@
         <v>0.8427340874867735</v>
       </c>
       <c r="BE219" s="3" t="n">
-        <v>0.5913376584913064</v>
+        <v>1.200822374736014</v>
       </c>
       <c r="BF219" s="3" t="n">
         <v>0.05635535793109901</v>
@@ -44190,7 +44206,7 @@
         <v>0.5099374101529588</v>
       </c>
       <c r="AM220" s="3" t="n">
-        <v>1.427408476381345</v>
+        <v>1.318670441650421</v>
       </c>
       <c r="AN220" s="3" t="n">
         <v>-0.1857476669569533</v>
@@ -44244,7 +44260,7 @@
         <v>0.8581433161443625</v>
       </c>
       <c r="BE220" s="3" t="n">
-        <v>0.5859266408701301</v>
+        <v>0.6978400369382251</v>
       </c>
       <c r="BF220" s="3" t="n">
         <v>0.1142390489483161</v>
@@ -44393,7 +44409,7 @@
         <v>0.104442641191315</v>
       </c>
       <c r="AM221" s="3" t="n">
-        <v>1.693785540921058</v>
+        <v>1.951591025400873</v>
       </c>
       <c r="AN221" s="3" t="n">
         <v>-0.0653312161169548</v>
@@ -44447,7 +44463,7 @@
         <v>0.8540292459698792</v>
       </c>
       <c r="BE221" s="3" t="n">
-        <v>0.6624007415556548</v>
+        <v>1.137363862998821</v>
       </c>
       <c r="BF221" s="3" t="n">
         <v>0.07884002274430027</v>
@@ -44596,7 +44612,7 @@
         <v>0.06007955019280872</v>
       </c>
       <c r="AM222" s="3" t="n">
-        <v>1.750266027180101</v>
+        <v>1.969409095324254</v>
       </c>
       <c r="AN222" s="3" t="n">
         <v>-0.05487986697048586</v>
@@ -44650,7 +44666,7 @@
         <v>0.854054060729489</v>
       </c>
       <c r="BE222" s="3" t="n">
-        <v>0.5852879245212794</v>
+        <v>1.121716015219447</v>
       </c>
       <c r="BF222" s="3" t="n">
         <v>0.06830067051403432</v>
@@ -44799,7 +44815,7 @@
         <v>0.9211098965057867</v>
       </c>
       <c r="AM223" s="3" t="n">
-        <v>1.314291073821078</v>
+        <v>0.8069844286592813</v>
       </c>
       <c r="AN223" s="3" t="n">
         <v>-0.2516623200621756</v>
@@ -44853,7 +44869,7 @@
         <v>0.8331881574783618</v>
       </c>
       <c r="BE223" s="3" t="n">
-        <v>0.2756799967763073</v>
+        <v>0.2756700517798301</v>
       </c>
       <c r="BF223" s="3" t="n">
         <v>0.108734733552331</v>
@@ -45002,7 +45018,7 @@
         <v>0.6582835737465704</v>
       </c>
       <c r="AM224" s="3" t="n">
-        <v>1.758031376006605</v>
+        <v>0.9414865024383248</v>
       </c>
       <c r="AN224" s="3" t="n">
         <v>0.1642143298896883</v>
@@ -45056,7 +45072,7 @@
         <v>0.8347085597949727</v>
       </c>
       <c r="BE224" s="3" t="n">
-        <v>-0.01769859082772434</v>
+        <v>-0.01963635050982194</v>
       </c>
       <c r="BF224" s="3" t="n">
         <v>0.10520255295427</v>
@@ -45205,7 +45221,7 @@
         <v>0.2671872578172995</v>
       </c>
       <c r="AM225" s="3" t="n">
-        <v>1.604426876905639</v>
+        <v>0.1361339766886784</v>
       </c>
       <c r="AN225" s="3" t="n">
         <v>-0.06934472105495293</v>
@@ -45259,7 +45275,7 @@
         <v>0.8390404581910493</v>
       </c>
       <c r="BE225" s="3" t="n">
-        <v>-0.4516034793079744</v>
+        <v>-0.6314071012366645</v>
       </c>
       <c r="BF225" s="3" t="n">
         <v>0.09072745013186675</v>
@@ -45438,7 +45454,7 @@
         <v>0.834961710296001</v>
       </c>
       <c r="BE226" s="3" t="n">
-        <v>0.1611427835287552</v>
+        <v>0.1611345342024546</v>
       </c>
       <c r="BF226" s="3" t="n">
         <v>0.1076445939752987</v>
@@ -45577,7 +45593,7 @@
         <v>0.02720966755339988</v>
       </c>
       <c r="AM227" s="3" t="n">
-        <v>1.828103744484007</v>
+        <v>-4.497966148527291</v>
       </c>
       <c r="AN227" s="3" t="n">
         <v>-0.0357593209828817</v>
@@ -45631,7 +45647,7 @@
         <v>0.820950952828032</v>
       </c>
       <c r="BE227" s="3" t="n">
-        <v>-5.393078261005174</v>
+        <v>-5.394138360277854</v>
       </c>
       <c r="BF227" s="3" t="n">
         <v>0.03638685244918782</v>
@@ -45780,7 +45796,7 @@
         <v>0.2967248331585669</v>
       </c>
       <c r="AM228" s="3" t="n">
-        <v>1.600501945647358</v>
+        <v>0.1893635539131761</v>
       </c>
       <c r="AN228" s="3" t="n">
         <v>-0.0662697844350455</v>
@@ -45834,7 +45850,7 @@
         <v>0.827423373354135</v>
       </c>
       <c r="BE228" s="3" t="n">
-        <v>-0.577707889865495</v>
+        <v>-0.5777525266929804</v>
       </c>
       <c r="BF228" s="3" t="n">
         <v>0.08578861470421656</v>
@@ -45983,7 +45999,7 @@
         <v>0.5667948177665066</v>
       </c>
       <c r="AM229" s="3" t="n">
-        <v>1.551424083259953</v>
+        <v>0.7487112148942008</v>
       </c>
       <c r="AN229" s="3" t="n">
         <v>-0.05400165347155095</v>
@@ -46385,7 +46401,7 @@
         <v>0.8451529242944911</v>
       </c>
       <c r="BE231" s="3" t="n">
-        <v>0.3513374470001395</v>
+        <v>0.3755430030819628</v>
       </c>
       <c r="BF231" s="3" t="n">
         <v>0.1095434273135942</v>
@@ -46524,7 +46540,7 @@
         <v>0.2858265171812326</v>
       </c>
       <c r="AM232" s="3" t="n">
-        <v>1.600643897087242</v>
+        <v>1.205862080003024</v>
       </c>
       <c r="AN232" s="3" t="n">
         <v>-0.07060422380018838</v>
@@ -46578,7 +46594,7 @@
         <v>0.8489697157710339</v>
       </c>
       <c r="BE232" s="3" t="n">
-        <v>0.3232395723925313</v>
+        <v>0.440842243359497</v>
       </c>
       <c r="BF232" s="3" t="n">
         <v>0.09631116905478565</v>
@@ -46727,7 +46743,7 @@
         <v>0.1013031975777293</v>
       </c>
       <c r="AM233" s="3" t="n">
-        <v>1.701665919446477</v>
+        <v>1.222140512984446</v>
       </c>
       <c r="AN233" s="3" t="n">
         <v>-0.06191941253706246</v>
@@ -46781,7 +46797,7 @@
         <v>0.8458706793308165</v>
       </c>
       <c r="BE233" s="3" t="n">
-        <v>0.2348225793723825</v>
+        <v>0.4022672595297385</v>
       </c>
       <c r="BF233" s="3" t="n">
         <v>0.07312297336076728</v>
@@ -46930,7 +46946,7 @@
         <v>0.04303337829368609</v>
       </c>
       <c r="AM234" s="3" t="n">
-        <v>1.785558881257877</v>
+        <v>1.198126326173434</v>
       </c>
       <c r="AN234" s="3" t="n">
         <v>-0.04652741651663161</v>
@@ -46984,7 +47000,7 @@
         <v>0.8444557929555723</v>
       </c>
       <c r="BE234" s="3" t="n">
-        <v>0.1612037163284335</v>
+        <v>0.3286105938028109</v>
       </c>
       <c r="BF234" s="3" t="n">
         <v>0.05698600908519477</v>
@@ -47133,7 +47149,7 @@
         <v>0.02768445579062015</v>
       </c>
       <c r="AM235" s="3" t="n">
-        <v>1.825708514861803</v>
+        <v>1.20912088399836</v>
       </c>
       <c r="AN235" s="3" t="n">
         <v>-0.0377667857340761</v>
@@ -47187,7 +47203,7 @@
         <v>0.8365944007060556</v>
       </c>
       <c r="BE235" s="3" t="n">
-        <v>0.1442157568911842</v>
+        <v>0.3151500194344964</v>
       </c>
       <c r="BF235" s="3" t="n">
         <v>0.04525233016120642</v>
